--- a/itens.xlsx
+++ b/itens.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodol\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D350023-06FB-4B50-8738-C0372AC13936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6D2170-D52C-4DD2-898A-0587549828BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FE85E5DB-FB4E-4537-9CA3-68884499EC91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FE85E5DB-FB4E-4537-9CA3-68884499EC91}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3005" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1072">
   <si>
     <t>idCompra</t>
   </si>
@@ -2021,15 +2021,6 @@
     <t>MEMÃ“RIA RAM, REFERÃŠNCIA: PC3-12800 , APLICAÃ‡ÃƒO: MICROCOMPUTADORES , CAPACIDADE MEMÃ“RIA: 8 GB, PADRÃƒO: DDR3"</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1600 Mhz"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 240-Pinos"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CL-11 </t>
-  </si>
-  <si>
     <t>5,96481E+13</t>
   </si>
   <si>
@@ -2367,12 +2358,6 @@
   </si>
   <si>
     <t>EQUIPAMENTO WIRELESS, PADRÃƒO: IEEE 802.11ax (Wi-Fi 6) , TAXA TRANSMISSÃƒO: 574 Mbps - 1201 Mbps MBPS, FREQUÃŠNCIA: 2.4 GHz - 5 GHZ, APLICAÃ‡ÃƒO: CONTROLE DE REDE WI FI , CONEXÃƒO: RJ-45 c/PoE+ (802.3at) , CARACTERÃSTICAS ADICIONAIS: Dual-Band"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MÃ­nima de 1775 Mbps (AX1800)"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Teto/ , TIPO: ACCESS POINT WI-FI 6 </t>
   </si>
   <si>
     <t>5,30211E+13</t>
@@ -3641,15 +3626,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFFA29C-BB4B-4FCC-8D34-B96F66D3F3FB}">
-  <dimension ref="A1:AL149"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI149"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="30.140625" customWidth="1"/>
-    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" customWidth="1"/>
+    <col min="8" max="8" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3756,7 +3741,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
@@ -3860,7 +3845,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
@@ -3964,7 +3949,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>53</v>
       </c>
@@ -4068,7 +4053,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
@@ -4172,7 +4157,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>78</v>
       </c>
@@ -4276,7 +4261,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
@@ -4380,7 +4365,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>78</v>
       </c>
@@ -4484,7 +4469,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>91</v>
       </c>
@@ -4588,7 +4573,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>101</v>
       </c>
@@ -4692,7 +4677,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>111</v>
       </c>
@@ -4796,7 +4781,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>122</v>
       </c>
@@ -4900,7 +4885,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>122</v>
       </c>
@@ -5004,7 +4989,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>134</v>
       </c>
@@ -5108,7 +5093,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>144</v>
       </c>
@@ -5212,7 +5197,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>152</v>
       </c>
@@ -5316,7 +5301,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>160</v>
       </c>
@@ -5420,7 +5405,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>168</v>
       </c>
@@ -5521,7 +5506,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>176</v>
       </c>
@@ -5625,7 +5610,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>176</v>
       </c>
@@ -5729,7 +5714,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>176</v>
       </c>
@@ -5833,7 +5818,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>187</v>
       </c>
@@ -5937,7 +5922,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>198</v>
       </c>
@@ -6041,7 +6026,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>206</v>
       </c>
@@ -6145,7 +6130,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>214</v>
       </c>
@@ -6249,7 +6234,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>214</v>
       </c>
@@ -6353,7 +6338,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>187</v>
       </c>
@@ -6457,7 +6442,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>231</v>
       </c>
@@ -6561,7 +6546,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>231</v>
       </c>
@@ -6665,7 +6650,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>245</v>
       </c>
@@ -6769,7 +6754,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>255</v>
       </c>
@@ -6873,7 +6858,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>265</v>
       </c>
@@ -6977,7 +6962,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>275</v>
       </c>
@@ -7081,7 +7066,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>284</v>
       </c>
@@ -7185,7 +7170,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
@@ -7289,7 +7274,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>294</v>
       </c>
@@ -7393,7 +7378,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>304</v>
       </c>
@@ -7497,7 +7482,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>312</v>
       </c>
@@ -7601,7 +7586,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>318</v>
       </c>
@@ -7705,7 +7690,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>318</v>
       </c>
@@ -7809,7 +7794,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>328</v>
       </c>
@@ -7913,7 +7898,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>336</v>
       </c>
@@ -8017,7 +8002,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>346</v>
       </c>
@@ -8121,7 +8106,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>355</v>
       </c>
@@ -8225,7 +8210,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>363</v>
       </c>
@@ -8329,7 +8314,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>372</v>
       </c>
@@ -8433,7 +8418,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>378</v>
       </c>
@@ -8537,7 +8522,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>388</v>
       </c>
@@ -8641,7 +8626,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>398</v>
       </c>
@@ -8745,7 +8730,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>407</v>
       </c>
@@ -8849,7 +8834,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>415</v>
       </c>
@@ -8950,7 +8935,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>336</v>
       </c>
@@ -9054,7 +9039,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>346</v>
       </c>
@@ -9158,7 +9143,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>355</v>
       </c>
@@ -9262,7 +9247,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>363</v>
       </c>
@@ -9366,7 +9351,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>372</v>
       </c>
@@ -9470,7 +9455,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>378</v>
       </c>
@@ -9574,7 +9559,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>388</v>
       </c>
@@ -9678,7 +9663,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>398</v>
       </c>
@@ -9782,7 +9767,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>407</v>
       </c>
@@ -9886,7 +9871,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>415</v>
       </c>
@@ -9987,7 +9972,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>430</v>
       </c>
@@ -10091,7 +10076,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>442</v>
       </c>
@@ -10195,7 +10180,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>451</v>
       </c>
@@ -10296,7 +10281,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>460</v>
       </c>
@@ -10400,7 +10385,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>467</v>
       </c>
@@ -10504,7 +10489,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>475</v>
       </c>
@@ -10608,7 +10593,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>485</v>
       </c>
@@ -10712,7 +10697,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>492</v>
       </c>
@@ -10816,7 +10801,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>502</v>
       </c>
@@ -10920,7 +10905,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>511</v>
       </c>
@@ -11024,7 +11009,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>521</v>
       </c>
@@ -11128,7 +11113,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>527</v>
       </c>
@@ -11232,7 +11217,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>535</v>
       </c>
@@ -11336,7 +11321,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>544</v>
       </c>
@@ -11440,7 +11425,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>551</v>
       </c>
@@ -11544,7 +11529,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>561</v>
       </c>
@@ -11648,7 +11633,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>570</v>
       </c>
@@ -11752,7 +11737,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>578</v>
       </c>
@@ -11856,7 +11841,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>586</v>
       </c>
@@ -11960,7 +11945,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>589</v>
       </c>
@@ -12064,7 +12049,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>599</v>
       </c>
@@ -12168,7 +12153,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>607</v>
       </c>
@@ -12272,7 +12257,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>617</v>
       </c>
@@ -12376,7 +12361,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>626</v>
       </c>
@@ -12480,7 +12465,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>634</v>
       </c>
@@ -12584,7 +12569,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>643</v>
       </c>
@@ -12688,7 +12673,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>652</v>
       </c>
@@ -12792,7 +12777,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>659</v>
       </c>
@@ -12814,100 +12799,91 @@
       <c r="G89" t="s">
         <v>660</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89">
+        <v>632556</v>
+      </c>
+      <c r="I89" t="s">
+        <v>38</v>
+      </c>
+      <c r="K89" t="s">
+        <v>39</v>
+      </c>
+      <c r="L89" t="s">
+        <v>40</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>5</v>
+      </c>
+      <c r="O89">
+        <v>176</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="I89" t="s">
+      <c r="R89" t="s">
         <v>662</v>
       </c>
-      <c r="J89" t="s">
+      <c r="S89" t="s">
+        <v>470</v>
+      </c>
+      <c r="T89">
+        <v>929716</v>
+      </c>
+      <c r="U89" t="s">
         <v>663</v>
       </c>
-      <c r="K89">
-        <v>632556</v>
-      </c>
-      <c r="L89" t="s">
-        <v>38</v>
-      </c>
-      <c r="N89" t="s">
-        <v>39</v>
-      </c>
-      <c r="O89" t="s">
-        <v>40</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>5</v>
-      </c>
-      <c r="R89">
-        <v>176</v>
-      </c>
-      <c r="S89">
-        <v>0</v>
-      </c>
-      <c r="T89" s="1" t="s">
+      <c r="V89">
+        <v>3543402</v>
+      </c>
+      <c r="W89" t="s">
+        <v>410</v>
+      </c>
+      <c r="X89" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y89">
+        <v>96048</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>663</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>46054</v>
+      </c>
+      <c r="AD89" t="s">
         <v>664</v>
       </c>
-      <c r="U89" t="s">
+      <c r="AE89" t="s">
         <v>665</v>
       </c>
-      <c r="V89" t="s">
-        <v>470</v>
-      </c>
-      <c r="W89">
-        <v>929716</v>
-      </c>
-      <c r="X89" t="s">
+      <c r="AF89" s="3">
+        <v>46065</v>
+      </c>
+      <c r="AG89" t="s">
         <v>666</v>
       </c>
-      <c r="Y89">
-        <v>3543402</v>
-      </c>
-      <c r="Z89" t="s">
-        <v>410</v>
-      </c>
-      <c r="AA89" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB89">
-        <v>96048</v>
-      </c>
-      <c r="AC89" t="s">
-        <v>666</v>
-      </c>
-      <c r="AD89" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE89" t="s">
-        <v>140</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>46054</v>
-      </c>
-      <c r="AG89" t="s">
+      <c r="AH89">
+        <v>7060</v>
+      </c>
+      <c r="AI89" t="s">
         <v>667</v>
       </c>
-      <c r="AH89" t="s">
+    </row>
+    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>668</v>
-      </c>
-      <c r="AI89" s="3">
-        <v>46065</v>
-      </c>
-      <c r="AJ89" t="s">
-        <v>669</v>
-      </c>
-      <c r="AK89">
-        <v>7060</v>
-      </c>
-      <c r="AL89" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>671</v>
       </c>
       <c r="B90">
         <v>10891272</v>
@@ -12927,100 +12903,91 @@
       <c r="G90" t="s">
         <v>660</v>
       </c>
-      <c r="H90" t="s">
-        <v>661</v>
+      <c r="H90">
+        <v>632556</v>
       </c>
       <c r="I90" t="s">
-        <v>662</v>
-      </c>
-      <c r="J90" t="s">
-        <v>663</v>
-      </c>
-      <c r="K90">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K90" t="s">
+        <v>39</v>
       </c>
       <c r="L90" t="s">
-        <v>38</v>
-      </c>
-      <c r="N90" t="s">
-        <v>39</v>
-      </c>
-      <c r="O90" t="s">
         <v>40</v>
       </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>100</v>
+      </c>
+      <c r="O90">
+        <v>135</v>
+      </c>
       <c r="P90">
         <v>0</v>
       </c>
-      <c r="Q90">
-        <v>100</v>
-      </c>
-      <c r="R90">
-        <v>135</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-      <c r="T90" s="1" t="s">
+      <c r="Q90" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="R90" t="s">
+        <v>670</v>
+      </c>
+      <c r="S90" t="s">
+        <v>671</v>
+      </c>
+      <c r="T90">
+        <v>453714</v>
+      </c>
+      <c r="U90" t="s">
         <v>672</v>
       </c>
-      <c r="U90" t="s">
+      <c r="V90">
+        <v>5002704</v>
+      </c>
+      <c r="W90" t="s">
+        <v>116</v>
+      </c>
+      <c r="X90" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y90">
+        <v>97186</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>672</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC90" s="3">
+        <v>46063</v>
+      </c>
+      <c r="AD90" t="s">
         <v>673</v>
       </c>
-      <c r="V90" t="s">
+      <c r="AE90" t="s">
         <v>674</v>
-      </c>
-      <c r="W90">
-        <v>453714</v>
-      </c>
-      <c r="X90" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y90">
-        <v>5002704</v>
-      </c>
-      <c r="Z90" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA90" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB90">
-        <v>97186</v>
-      </c>
-      <c r="AC90" t="s">
-        <v>675</v>
-      </c>
-      <c r="AD90" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE90" t="s">
-        <v>140</v>
       </c>
       <c r="AF90" s="3">
         <v>46063</v>
       </c>
       <c r="AG90" t="s">
-        <v>676</v>
-      </c>
-      <c r="AH90" t="s">
-        <v>677</v>
-      </c>
-      <c r="AI90" s="3">
-        <v>46063</v>
-      </c>
-      <c r="AJ90" t="s">
         <v>520</v>
       </c>
-      <c r="AK90">
+      <c r="AH90">
         <v>7060</v>
       </c>
-      <c r="AL90" t="s">
-        <v>670</v>
+      <c r="AI90" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B91">
         <v>10869126</v>
@@ -13040,100 +13007,91 @@
       <c r="G91" t="s">
         <v>660</v>
       </c>
-      <c r="H91" t="s">
-        <v>661</v>
+      <c r="H91">
+        <v>632556</v>
       </c>
       <c r="I91" t="s">
-        <v>662</v>
-      </c>
-      <c r="J91" t="s">
-        <v>663</v>
-      </c>
-      <c r="K91">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K91" t="s">
+        <v>39</v>
       </c>
       <c r="L91" t="s">
-        <v>38</v>
-      </c>
-      <c r="N91" t="s">
-        <v>39</v>
-      </c>
-      <c r="O91" t="s">
         <v>40</v>
       </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>50</v>
+      </c>
+      <c r="O91">
+        <v>229</v>
+      </c>
       <c r="P91">
         <v>0</v>
       </c>
-      <c r="Q91">
-        <v>50</v>
-      </c>
-      <c r="R91">
-        <v>229</v>
-      </c>
-      <c r="S91">
-        <v>0</v>
-      </c>
-      <c r="T91" s="1" t="s">
+      <c r="Q91" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="R91" t="s">
+        <v>677</v>
+      </c>
+      <c r="S91" t="s">
+        <v>678</v>
+      </c>
+      <c r="T91">
+        <v>987971</v>
+      </c>
+      <c r="U91" t="s">
         <v>679</v>
       </c>
-      <c r="U91" t="s">
+      <c r="V91">
+        <v>4123501</v>
+      </c>
+      <c r="W91" t="s">
         <v>680</v>
       </c>
-      <c r="V91" t="s">
+      <c r="X91" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y91">
+        <v>98137</v>
+      </c>
+      <c r="Z91" t="s">
         <v>681</v>
       </c>
-      <c r="W91">
-        <v>987971</v>
-      </c>
-      <c r="X91" t="s">
+      <c r="AA91" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB91" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>46059</v>
+      </c>
+      <c r="AD91" t="s">
         <v>682</v>
       </c>
-      <c r="Y91">
-        <v>4123501</v>
-      </c>
-      <c r="Z91" t="s">
+      <c r="AE91" t="s">
         <v>683</v>
-      </c>
-      <c r="AA91" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB91">
-        <v>98137</v>
-      </c>
-      <c r="AC91" t="s">
-        <v>684</v>
-      </c>
-      <c r="AD91" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE91" t="s">
-        <v>140</v>
       </c>
       <c r="AF91" s="3">
         <v>46059</v>
       </c>
       <c r="AG91" t="s">
-        <v>685</v>
-      </c>
-      <c r="AH91" t="s">
-        <v>686</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>46059</v>
-      </c>
-      <c r="AJ91" t="s">
         <v>88</v>
       </c>
-      <c r="AK91">
+      <c r="AH91">
         <v>7060</v>
       </c>
-      <c r="AL91" t="s">
-        <v>670</v>
+      <c r="AI91" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B92">
         <v>10709628</v>
@@ -13153,100 +13111,91 @@
       <c r="G92" t="s">
         <v>660</v>
       </c>
-      <c r="H92" t="s">
-        <v>661</v>
+      <c r="H92">
+        <v>632556</v>
       </c>
       <c r="I92" t="s">
-        <v>662</v>
-      </c>
-      <c r="J92" t="s">
-        <v>663</v>
-      </c>
-      <c r="K92">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K92" t="s">
+        <v>39</v>
       </c>
       <c r="L92" t="s">
-        <v>38</v>
-      </c>
-      <c r="N92" t="s">
-        <v>39</v>
-      </c>
-      <c r="O92" t="s">
         <v>40</v>
       </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>10</v>
+      </c>
+      <c r="O92">
+        <v>112.75</v>
+      </c>
       <c r="P92">
         <v>0</v>
       </c>
-      <c r="Q92">
-        <v>10</v>
-      </c>
-      <c r="R92">
-        <v>112.75</v>
-      </c>
-      <c r="S92">
-        <v>0</v>
-      </c>
-      <c r="T92" s="1" t="s">
+      <c r="Q92" s="1" t="s">
         <v>487</v>
       </c>
+      <c r="R92" t="s">
+        <v>488</v>
+      </c>
+      <c r="S92" t="s">
+        <v>685</v>
+      </c>
+      <c r="T92">
+        <v>988675</v>
+      </c>
       <c r="U92" t="s">
-        <v>488</v>
-      </c>
-      <c r="V92" t="s">
+        <v>686</v>
+      </c>
+      <c r="V92">
+        <v>4319802</v>
+      </c>
+      <c r="W92" t="s">
+        <v>687</v>
+      </c>
+      <c r="X92" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y92">
+        <v>96803</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>686</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB92" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>46038</v>
+      </c>
+      <c r="AD92" t="s">
         <v>688</v>
       </c>
-      <c r="W92">
-        <v>988675</v>
-      </c>
-      <c r="X92" t="s">
+      <c r="AE92" t="s">
         <v>689</v>
-      </c>
-      <c r="Y92">
-        <v>4319802</v>
-      </c>
-      <c r="Z92" t="s">
-        <v>690</v>
-      </c>
-      <c r="AA92" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB92">
-        <v>96803</v>
-      </c>
-      <c r="AC92" t="s">
-        <v>689</v>
-      </c>
-      <c r="AD92" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE92" t="s">
-        <v>140</v>
       </c>
       <c r="AF92" s="3">
         <v>46038</v>
       </c>
       <c r="AG92" t="s">
-        <v>691</v>
-      </c>
-      <c r="AH92" t="s">
-        <v>692</v>
-      </c>
-      <c r="AI92" s="3">
-        <v>46038</v>
-      </c>
-      <c r="AJ92" t="s">
         <v>633</v>
       </c>
-      <c r="AK92">
+      <c r="AH92">
         <v>7060</v>
       </c>
-      <c r="AL92" t="s">
-        <v>670</v>
+      <c r="AI92" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B93">
         <v>10571640</v>
@@ -13266,100 +13215,91 @@
       <c r="G93" t="s">
         <v>660</v>
       </c>
-      <c r="H93" t="s">
-        <v>661</v>
+      <c r="H93">
+        <v>632556</v>
       </c>
       <c r="I93" t="s">
-        <v>662</v>
-      </c>
-      <c r="J93" t="s">
-        <v>663</v>
-      </c>
-      <c r="K93">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K93" t="s">
+        <v>39</v>
       </c>
       <c r="L93" t="s">
-        <v>38</v>
-      </c>
-      <c r="N93" t="s">
-        <v>39</v>
-      </c>
-      <c r="O93" t="s">
         <v>40</v>
       </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>20</v>
+      </c>
+      <c r="O93">
+        <v>162</v>
+      </c>
       <c r="P93">
         <v>0</v>
       </c>
-      <c r="Q93">
-        <v>20</v>
-      </c>
-      <c r="R93">
-        <v>162</v>
-      </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-      <c r="T93" s="1" t="s">
+      <c r="Q93" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="R93" t="s">
+        <v>692</v>
+      </c>
+      <c r="S93" t="s">
+        <v>693</v>
+      </c>
+      <c r="T93">
+        <v>380197</v>
+      </c>
+      <c r="U93" t="s">
         <v>694</v>
       </c>
-      <c r="U93" t="s">
+      <c r="V93">
+        <v>3551405</v>
+      </c>
+      <c r="W93" t="s">
         <v>695</v>
       </c>
-      <c r="V93" t="s">
+      <c r="X93" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y93">
+        <v>95602</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>481</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB93" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>46014</v>
+      </c>
+      <c r="AD93" t="s">
         <v>696</v>
       </c>
-      <c r="W93">
-        <v>380197</v>
-      </c>
-      <c r="X93" t="s">
+      <c r="AE93" t="s">
         <v>697</v>
-      </c>
-      <c r="Y93">
-        <v>3551405</v>
-      </c>
-      <c r="Z93" t="s">
-        <v>698</v>
-      </c>
-      <c r="AA93" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB93">
-        <v>95602</v>
-      </c>
-      <c r="AC93" t="s">
-        <v>481</v>
-      </c>
-      <c r="AD93" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE93" t="s">
-        <v>48</v>
       </c>
       <c r="AF93" s="3">
         <v>46014</v>
       </c>
       <c r="AG93" t="s">
-        <v>699</v>
-      </c>
-      <c r="AH93" t="s">
-        <v>700</v>
-      </c>
-      <c r="AI93" s="3">
-        <v>46014</v>
-      </c>
-      <c r="AJ93" t="s">
         <v>484</v>
       </c>
-      <c r="AK93">
+      <c r="AH93">
         <v>7060</v>
       </c>
-      <c r="AL93" t="s">
-        <v>670</v>
+      <c r="AI93" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B94">
         <v>10497715</v>
@@ -13379,100 +13319,91 @@
       <c r="G94" t="s">
         <v>660</v>
       </c>
-      <c r="H94" t="s">
-        <v>661</v>
+      <c r="H94">
+        <v>632556</v>
       </c>
       <c r="I94" t="s">
-        <v>662</v>
-      </c>
-      <c r="J94" t="s">
-        <v>663</v>
-      </c>
-      <c r="K94">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K94" t="s">
+        <v>39</v>
       </c>
       <c r="L94" t="s">
-        <v>38</v>
-      </c>
-      <c r="N94" t="s">
-        <v>39</v>
-      </c>
-      <c r="O94" t="s">
         <v>40</v>
       </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>10</v>
+      </c>
+      <c r="O94">
+        <v>103.97</v>
+      </c>
       <c r="P94">
         <v>0</v>
       </c>
-      <c r="Q94">
-        <v>10</v>
-      </c>
-      <c r="R94">
-        <v>103.97</v>
-      </c>
-      <c r="S94">
-        <v>0</v>
-      </c>
-      <c r="T94" s="1" t="s">
+      <c r="Q94" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="R94" t="s">
+        <v>700</v>
+      </c>
+      <c r="S94" t="s">
+        <v>701</v>
+      </c>
+      <c r="T94">
+        <v>929576</v>
+      </c>
+      <c r="U94" t="s">
         <v>702</v>
       </c>
-      <c r="U94" t="s">
+      <c r="V94">
+        <v>4106407</v>
+      </c>
+      <c r="W94" t="s">
         <v>703</v>
       </c>
-      <c r="V94" t="s">
+      <c r="X94" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y94">
+        <v>96203</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>702</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB94" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>46010</v>
+      </c>
+      <c r="AD94" t="s">
         <v>704</v>
       </c>
-      <c r="W94">
-        <v>929576</v>
-      </c>
-      <c r="X94" t="s">
+      <c r="AE94" t="s">
         <v>705</v>
-      </c>
-      <c r="Y94">
-        <v>4106407</v>
-      </c>
-      <c r="Z94" t="s">
-        <v>706</v>
-      </c>
-      <c r="AA94" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB94">
-        <v>96203</v>
-      </c>
-      <c r="AC94" t="s">
-        <v>705</v>
-      </c>
-      <c r="AD94" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE94" t="s">
-        <v>48</v>
       </c>
       <c r="AF94" s="3">
         <v>46010</v>
       </c>
       <c r="AG94" t="s">
+        <v>706</v>
+      </c>
+      <c r="AH94">
+        <v>7060</v>
+      </c>
+      <c r="AI94" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="AH94" t="s">
-        <v>708</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>46010</v>
-      </c>
-      <c r="AJ94" t="s">
-        <v>709</v>
-      </c>
-      <c r="AK94">
-        <v>7060</v>
-      </c>
-      <c r="AL94" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="B95">
         <v>10354157</v>
@@ -13492,100 +13423,91 @@
       <c r="G95" t="s">
         <v>660</v>
       </c>
-      <c r="H95" t="s">
-        <v>661</v>
+      <c r="H95">
+        <v>632556</v>
       </c>
       <c r="I95" t="s">
-        <v>662</v>
-      </c>
-      <c r="J95" t="s">
-        <v>663</v>
-      </c>
-      <c r="K95">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K95" t="s">
+        <v>39</v>
       </c>
       <c r="L95" t="s">
-        <v>38</v>
-      </c>
-      <c r="N95" t="s">
-        <v>39</v>
-      </c>
-      <c r="O95" t="s">
         <v>40</v>
       </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>32</v>
+      </c>
+      <c r="O95">
+        <v>90.36</v>
+      </c>
       <c r="P95">
         <v>0</v>
       </c>
-      <c r="Q95">
-        <v>32</v>
-      </c>
-      <c r="R95">
-        <v>90.36</v>
-      </c>
-      <c r="S95">
-        <v>0</v>
-      </c>
-      <c r="T95" s="1" t="s">
+      <c r="Q95" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="R95" t="s">
+        <v>709</v>
+      </c>
+      <c r="S95" t="s">
+        <v>710</v>
+      </c>
+      <c r="T95">
+        <v>771000</v>
+      </c>
+      <c r="U95" t="s">
+        <v>531</v>
+      </c>
+      <c r="V95">
+        <v>3304557</v>
+      </c>
+      <c r="W95" t="s">
+        <v>106</v>
+      </c>
+      <c r="X95" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y95">
+        <v>52131</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>351</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB95" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC95" s="3">
+        <v>45987</v>
+      </c>
+      <c r="AD95" t="s">
+        <v>532</v>
+      </c>
+      <c r="AE95" t="s">
         <v>711</v>
       </c>
-      <c r="U95" t="s">
+      <c r="AF95" s="3">
+        <v>45993</v>
+      </c>
+      <c r="AG95" t="s">
+        <v>534</v>
+      </c>
+      <c r="AH95">
+        <v>7060</v>
+      </c>
+      <c r="AI95" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="V95" t="s">
-        <v>713</v>
-      </c>
-      <c r="W95">
-        <v>771000</v>
-      </c>
-      <c r="X95" t="s">
-        <v>531</v>
-      </c>
-      <c r="Y95">
-        <v>3304557</v>
-      </c>
-      <c r="Z95" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA95" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB95">
-        <v>52131</v>
-      </c>
-      <c r="AC95" t="s">
-        <v>351</v>
-      </c>
-      <c r="AD95" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE95" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF95" s="3">
-        <v>45987</v>
-      </c>
-      <c r="AG95" t="s">
-        <v>532</v>
-      </c>
-      <c r="AH95" t="s">
-        <v>714</v>
-      </c>
-      <c r="AI95" s="3">
-        <v>45993</v>
-      </c>
-      <c r="AJ95" t="s">
-        <v>534</v>
-      </c>
-      <c r="AK95">
-        <v>7060</v>
-      </c>
-      <c r="AL95" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="B96">
         <v>10346919</v>
@@ -13605,100 +13527,91 @@
       <c r="G96" t="s">
         <v>660</v>
       </c>
-      <c r="H96" t="s">
-        <v>661</v>
+      <c r="H96">
+        <v>632556</v>
       </c>
       <c r="I96" t="s">
-        <v>662</v>
-      </c>
-      <c r="J96" t="s">
-        <v>663</v>
-      </c>
-      <c r="K96">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K96" t="s">
+        <v>39</v>
       </c>
       <c r="L96" t="s">
-        <v>38</v>
-      </c>
-      <c r="N96" t="s">
-        <v>39</v>
-      </c>
-      <c r="O96" t="s">
         <v>40</v>
       </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>2</v>
+      </c>
+      <c r="O96">
+        <v>589.73</v>
+      </c>
       <c r="P96">
         <v>0</v>
       </c>
-      <c r="Q96">
-        <v>2</v>
-      </c>
-      <c r="R96">
-        <v>589.73</v>
-      </c>
-      <c r="S96">
-        <v>0</v>
-      </c>
-      <c r="T96" s="1" t="s">
+      <c r="Q96" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="R96" t="s">
+        <v>714</v>
+      </c>
+      <c r="S96" t="s">
+        <v>715</v>
+      </c>
+      <c r="T96">
+        <v>454524</v>
+      </c>
+      <c r="U96" t="s">
         <v>716</v>
       </c>
-      <c r="U96" t="s">
+      <c r="V96">
+        <v>4115408</v>
+      </c>
+      <c r="W96" t="s">
         <v>717</v>
       </c>
-      <c r="V96" t="s">
+      <c r="X96" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y96">
+        <v>97915</v>
+      </c>
+      <c r="Z96" t="s">
         <v>718</v>
       </c>
-      <c r="W96">
-        <v>454524</v>
-      </c>
-      <c r="X96" t="s">
+      <c r="AA96" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB96" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>45993</v>
+      </c>
+      <c r="AD96" t="s">
         <v>719</v>
       </c>
-      <c r="Y96">
-        <v>4115408</v>
-      </c>
-      <c r="Z96" t="s">
+      <c r="AE96" t="s">
         <v>720</v>
-      </c>
-      <c r="AA96" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB96">
-        <v>97915</v>
-      </c>
-      <c r="AC96" t="s">
-        <v>721</v>
-      </c>
-      <c r="AD96" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE96" t="s">
-        <v>140</v>
       </c>
       <c r="AF96" s="3">
         <v>45993</v>
       </c>
       <c r="AG96" t="s">
+        <v>721</v>
+      </c>
+      <c r="AH96">
+        <v>7060</v>
+      </c>
+      <c r="AI96" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="AH96" t="s">
-        <v>723</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>45993</v>
-      </c>
-      <c r="AJ96" t="s">
-        <v>724</v>
-      </c>
-      <c r="AK96">
-        <v>7060</v>
-      </c>
-      <c r="AL96" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>725</v>
       </c>
       <c r="B97">
         <v>10196890</v>
@@ -13718,100 +13631,91 @@
       <c r="G97" t="s">
         <v>660</v>
       </c>
-      <c r="H97" t="s">
-        <v>661</v>
+      <c r="H97">
+        <v>632556</v>
       </c>
       <c r="I97" t="s">
-        <v>662</v>
-      </c>
-      <c r="J97" t="s">
-        <v>663</v>
-      </c>
-      <c r="K97">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K97" t="s">
+        <v>39</v>
       </c>
       <c r="L97" t="s">
-        <v>38</v>
-      </c>
-      <c r="N97" t="s">
-        <v>39</v>
-      </c>
-      <c r="O97" t="s">
         <v>40</v>
       </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>40</v>
+      </c>
+      <c r="O97">
+        <v>90</v>
+      </c>
       <c r="P97">
         <v>0</v>
       </c>
-      <c r="Q97">
-        <v>40</v>
-      </c>
-      <c r="R97">
-        <v>90</v>
-      </c>
-      <c r="S97">
-        <v>0</v>
-      </c>
-      <c r="T97" s="1" t="s">
+      <c r="Q97" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="R97" t="s">
+        <v>724</v>
+      </c>
+      <c r="S97" t="s">
+        <v>725</v>
+      </c>
+      <c r="T97">
+        <v>981981</v>
+      </c>
+      <c r="U97" t="s">
         <v>726</v>
       </c>
-      <c r="U97" t="s">
+      <c r="V97">
+        <v>2504009</v>
+      </c>
+      <c r="W97" t="s">
         <v>727</v>
       </c>
-      <c r="V97" t="s">
+      <c r="X97" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y97">
+        <v>94606</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>726</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB97" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>45977</v>
+      </c>
+      <c r="AD97" t="s">
         <v>728</v>
       </c>
-      <c r="W97">
-        <v>981981</v>
-      </c>
-      <c r="X97" t="s">
+      <c r="AE97" t="s">
         <v>729</v>
       </c>
-      <c r="Y97">
-        <v>2504009</v>
-      </c>
-      <c r="Z97" t="s">
+      <c r="AF97" s="3">
+        <v>45978</v>
+      </c>
+      <c r="AG97" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH97">
+        <v>7060</v>
+      </c>
+      <c r="AI97" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="AA97" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB97">
-        <v>94606</v>
-      </c>
-      <c r="AC97" t="s">
-        <v>729</v>
-      </c>
-      <c r="AD97" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE97" t="s">
-        <v>140</v>
-      </c>
-      <c r="AF97" s="3">
-        <v>45977</v>
-      </c>
-      <c r="AG97" t="s">
-        <v>731</v>
-      </c>
-      <c r="AH97" t="s">
-        <v>732</v>
-      </c>
-      <c r="AI97" s="3">
-        <v>45978</v>
-      </c>
-      <c r="AJ97" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK97">
-        <v>7060</v>
-      </c>
-      <c r="AL97" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>733</v>
       </c>
       <c r="B98">
         <v>10103611</v>
@@ -13831,100 +13735,91 @@
       <c r="G98" t="s">
         <v>660</v>
       </c>
-      <c r="H98" t="s">
-        <v>661</v>
+      <c r="H98">
+        <v>632556</v>
       </c>
       <c r="I98" t="s">
-        <v>662</v>
-      </c>
-      <c r="J98" t="s">
-        <v>663</v>
-      </c>
-      <c r="K98">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K98" t="s">
+        <v>39</v>
       </c>
       <c r="L98" t="s">
-        <v>38</v>
-      </c>
-      <c r="N98" t="s">
-        <v>39</v>
-      </c>
-      <c r="O98" t="s">
         <v>40</v>
       </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>15</v>
+      </c>
+      <c r="O98">
+        <v>120</v>
+      </c>
       <c r="P98">
         <v>0</v>
       </c>
-      <c r="Q98">
-        <v>15</v>
-      </c>
-      <c r="R98">
-        <v>120</v>
-      </c>
-      <c r="S98">
-        <v>0</v>
-      </c>
-      <c r="T98" s="1" t="s">
+      <c r="Q98" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="R98" t="s">
+        <v>732</v>
+      </c>
+      <c r="S98" t="s">
+        <v>733</v>
+      </c>
+      <c r="T98">
+        <v>380225</v>
+      </c>
+      <c r="U98" t="s">
         <v>734</v>
       </c>
-      <c r="U98" t="s">
+      <c r="V98">
+        <v>3529401</v>
+      </c>
+      <c r="W98" t="s">
         <v>735</v>
       </c>
-      <c r="V98" t="s">
+      <c r="X98" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y98">
+        <v>95602</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>481</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB98" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>45970</v>
+      </c>
+      <c r="AD98" t="s">
         <v>736</v>
       </c>
-      <c r="W98">
-        <v>380225</v>
-      </c>
-      <c r="X98" t="s">
+      <c r="AE98" t="s">
         <v>737</v>
       </c>
-      <c r="Y98">
-        <v>3529401</v>
-      </c>
-      <c r="Z98" t="s">
+      <c r="AF98" s="3">
+        <v>45971</v>
+      </c>
+      <c r="AG98" t="s">
+        <v>484</v>
+      </c>
+      <c r="AH98">
+        <v>7060</v>
+      </c>
+      <c r="AI98" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="AA98" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB98">
-        <v>95602</v>
-      </c>
-      <c r="AC98" t="s">
-        <v>481</v>
-      </c>
-      <c r="AD98" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE98" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF98" s="3">
-        <v>45970</v>
-      </c>
-      <c r="AG98" t="s">
-        <v>739</v>
-      </c>
-      <c r="AH98" t="s">
-        <v>740</v>
-      </c>
-      <c r="AI98" s="3">
-        <v>45971</v>
-      </c>
-      <c r="AJ98" t="s">
-        <v>484</v>
-      </c>
-      <c r="AK98">
-        <v>7060</v>
-      </c>
-      <c r="AL98" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>741</v>
       </c>
       <c r="B99">
         <v>10087212</v>
@@ -13944,100 +13839,91 @@
       <c r="G99" t="s">
         <v>660</v>
       </c>
-      <c r="H99" t="s">
-        <v>661</v>
+      <c r="H99">
+        <v>632556</v>
       </c>
       <c r="I99" t="s">
-        <v>662</v>
-      </c>
-      <c r="J99" t="s">
-        <v>663</v>
-      </c>
-      <c r="K99">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K99" t="s">
+        <v>39</v>
       </c>
       <c r="L99" t="s">
+        <v>40</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
         <v>38</v>
       </c>
-      <c r="N99" t="s">
-        <v>39</v>
-      </c>
-      <c r="O99" t="s">
-        <v>40</v>
+      <c r="O99">
+        <v>70</v>
       </c>
       <c r="P99">
         <v>0</v>
       </c>
-      <c r="Q99">
-        <v>38</v>
-      </c>
-      <c r="R99">
-        <v>70</v>
-      </c>
-      <c r="S99">
-        <v>0</v>
-      </c>
-      <c r="T99" s="1" t="s">
+      <c r="Q99" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="R99" t="s">
+        <v>740</v>
+      </c>
+      <c r="S99" t="s">
+        <v>741</v>
+      </c>
+      <c r="T99">
+        <v>180101</v>
+      </c>
+      <c r="U99" t="s">
         <v>742</v>
       </c>
-      <c r="U99" t="s">
+      <c r="V99">
+        <v>3550308</v>
+      </c>
+      <c r="W99" t="s">
+        <v>271</v>
+      </c>
+      <c r="X99" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y99">
+        <v>95559</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>447</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB99" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>45968</v>
+      </c>
+      <c r="AD99" t="s">
         <v>743</v>
       </c>
-      <c r="V99" t="s">
+      <c r="AE99" t="s">
         <v>744</v>
-      </c>
-      <c r="W99">
-        <v>180101</v>
-      </c>
-      <c r="X99" t="s">
-        <v>745</v>
-      </c>
-      <c r="Y99">
-        <v>3550308</v>
-      </c>
-      <c r="Z99" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA99" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB99">
-        <v>95559</v>
-      </c>
-      <c r="AC99" t="s">
-        <v>447</v>
-      </c>
-      <c r="AD99" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE99" t="s">
-        <v>48</v>
       </c>
       <c r="AF99" s="3">
         <v>45968</v>
       </c>
       <c r="AG99" t="s">
-        <v>746</v>
-      </c>
-      <c r="AH99" t="s">
-        <v>747</v>
-      </c>
-      <c r="AI99" s="3">
-        <v>45968</v>
-      </c>
-      <c r="AJ99" t="s">
         <v>450</v>
       </c>
-      <c r="AK99">
+      <c r="AH99">
         <v>7060</v>
       </c>
-      <c r="AL99" t="s">
-        <v>670</v>
+      <c r="AI99" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B100">
         <v>10087240</v>
@@ -14057,100 +13943,91 @@
       <c r="G100" t="s">
         <v>660</v>
       </c>
-      <c r="H100" t="s">
-        <v>661</v>
+      <c r="H100">
+        <v>632556</v>
       </c>
       <c r="I100" t="s">
-        <v>662</v>
-      </c>
-      <c r="J100" t="s">
-        <v>663</v>
-      </c>
-      <c r="K100">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K100" t="s">
+        <v>39</v>
       </c>
       <c r="L100" t="s">
-        <v>38</v>
-      </c>
-      <c r="N100" t="s">
-        <v>39</v>
-      </c>
-      <c r="O100" t="s">
         <v>40</v>
       </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>12</v>
+      </c>
+      <c r="O100">
+        <v>70</v>
+      </c>
       <c r="P100">
         <v>0</v>
       </c>
-      <c r="Q100">
-        <v>12</v>
-      </c>
-      <c r="R100">
-        <v>70</v>
-      </c>
-      <c r="S100">
-        <v>0</v>
-      </c>
-      <c r="T100" s="1" t="s">
+      <c r="Q100" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="R100" t="s">
+        <v>740</v>
+      </c>
+      <c r="S100" t="s">
+        <v>741</v>
+      </c>
+      <c r="T100">
+        <v>180101</v>
+      </c>
+      <c r="U100" t="s">
         <v>742</v>
       </c>
-      <c r="U100" t="s">
+      <c r="V100">
+        <v>3550308</v>
+      </c>
+      <c r="W100" t="s">
+        <v>271</v>
+      </c>
+      <c r="X100" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y100">
+        <v>95559</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>447</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB100" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>45968</v>
+      </c>
+      <c r="AD100" t="s">
         <v>743</v>
       </c>
-      <c r="V100" t="s">
-        <v>744</v>
-      </c>
-      <c r="W100">
-        <v>180101</v>
-      </c>
-      <c r="X100" t="s">
+      <c r="AE100" t="s">
         <v>745</v>
-      </c>
-      <c r="Y100">
-        <v>3550308</v>
-      </c>
-      <c r="Z100" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA100" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB100">
-        <v>95559</v>
-      </c>
-      <c r="AC100" t="s">
-        <v>447</v>
-      </c>
-      <c r="AD100" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE100" t="s">
-        <v>48</v>
       </c>
       <c r="AF100" s="3">
         <v>45968</v>
       </c>
       <c r="AG100" t="s">
+        <v>450</v>
+      </c>
+      <c r="AH100">
+        <v>7060</v>
+      </c>
+      <c r="AI100" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="AH100" t="s">
-        <v>748</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>45968</v>
-      </c>
-      <c r="AJ100" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK100">
-        <v>7060</v>
-      </c>
-      <c r="AL100" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="B101">
         <v>10040996</v>
@@ -14170,100 +14047,91 @@
       <c r="G101" t="s">
         <v>660</v>
       </c>
-      <c r="H101" t="s">
-        <v>661</v>
+      <c r="H101">
+        <v>632556</v>
       </c>
       <c r="I101" t="s">
-        <v>662</v>
-      </c>
-      <c r="J101" t="s">
-        <v>663</v>
-      </c>
-      <c r="K101">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K101" t="s">
+        <v>39</v>
       </c>
       <c r="L101" t="s">
-        <v>38</v>
-      </c>
-      <c r="N101" t="s">
-        <v>39</v>
-      </c>
-      <c r="O101" t="s">
         <v>40</v>
       </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>20</v>
+      </c>
+      <c r="O101">
+        <v>54.8</v>
+      </c>
       <c r="P101">
         <v>0</v>
       </c>
-      <c r="Q101">
-        <v>20</v>
-      </c>
-      <c r="R101">
-        <v>54.8</v>
-      </c>
-      <c r="S101">
-        <v>0</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>694</v>
+      <c r="Q101" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="R101" t="s">
+        <v>692</v>
+      </c>
+      <c r="S101" t="s">
+        <v>693</v>
+      </c>
+      <c r="T101">
+        <v>380270</v>
       </c>
       <c r="U101" t="s">
-        <v>695</v>
-      </c>
-      <c r="V101" t="s">
-        <v>696</v>
-      </c>
-      <c r="W101">
-        <v>380270</v>
+        <v>747</v>
+      </c>
+      <c r="V101">
+        <v>3557006</v>
+      </c>
+      <c r="W101" t="s">
+        <v>748</v>
       </c>
       <c r="X101" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y101">
+        <v>95602</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>481</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>45965</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>749</v>
+      </c>
+      <c r="AE101" t="s">
         <v>750</v>
-      </c>
-      <c r="Y101">
-        <v>3557006</v>
-      </c>
-      <c r="Z101" t="s">
-        <v>751</v>
-      </c>
-      <c r="AA101" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB101">
-        <v>95602</v>
-      </c>
-      <c r="AC101" t="s">
-        <v>481</v>
-      </c>
-      <c r="AD101" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE101" t="s">
-        <v>48</v>
       </c>
       <c r="AF101" s="3">
         <v>45965</v>
       </c>
       <c r="AG101" t="s">
+        <v>751</v>
+      </c>
+      <c r="AH101">
+        <v>7060</v>
+      </c>
+      <c r="AI101" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="AH101" t="s">
-        <v>753</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>45965</v>
-      </c>
-      <c r="AJ101" t="s">
-        <v>754</v>
-      </c>
-      <c r="AK101">
-        <v>7060</v>
-      </c>
-      <c r="AL101" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="B102">
         <v>10041480</v>
@@ -14283,100 +14151,91 @@
       <c r="G102" t="s">
         <v>660</v>
       </c>
-      <c r="H102" t="s">
-        <v>661</v>
+      <c r="H102">
+        <v>632556</v>
       </c>
       <c r="I102" t="s">
-        <v>662</v>
-      </c>
-      <c r="J102" t="s">
-        <v>663</v>
-      </c>
-      <c r="K102">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K102" t="s">
+        <v>39</v>
       </c>
       <c r="L102" t="s">
-        <v>38</v>
-      </c>
-      <c r="N102" t="s">
-        <v>39</v>
-      </c>
-      <c r="O102" t="s">
         <v>40</v>
       </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>5</v>
+      </c>
+      <c r="O102">
+        <v>175</v>
+      </c>
       <c r="P102">
         <v>0</v>
       </c>
-      <c r="Q102">
-        <v>5</v>
-      </c>
-      <c r="R102">
-        <v>175</v>
-      </c>
-      <c r="S102">
-        <v>0</v>
-      </c>
-      <c r="T102" s="1" t="s">
+      <c r="Q102" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="R102" t="s">
+        <v>754</v>
+      </c>
+      <c r="S102" t="s">
+        <v>646</v>
+      </c>
+      <c r="T102">
+        <v>931465</v>
+      </c>
+      <c r="U102" t="s">
+        <v>755</v>
+      </c>
+      <c r="V102">
+        <v>2211001</v>
+      </c>
+      <c r="W102" t="s">
         <v>756</v>
       </c>
-      <c r="U102" t="s">
+      <c r="X102" t="s">
         <v>757</v>
       </c>
-      <c r="V102" t="s">
-        <v>646</v>
-      </c>
-      <c r="W102">
-        <v>931465</v>
-      </c>
-      <c r="X102" t="s">
+      <c r="Y102">
+        <v>85398</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>755</v>
+      </c>
+      <c r="AA102" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>45964</v>
+      </c>
+      <c r="AD102" t="s">
         <v>758</v>
       </c>
-      <c r="Y102">
-        <v>2211001</v>
-      </c>
-      <c r="Z102" t="s">
+      <c r="AE102" t="s">
         <v>759</v>
       </c>
-      <c r="AA102" t="s">
+      <c r="AF102" s="3">
+        <v>45961</v>
+      </c>
+      <c r="AG102" t="s">
         <v>760</v>
       </c>
-      <c r="AB102">
-        <v>85398</v>
-      </c>
-      <c r="AC102" t="s">
-        <v>758</v>
-      </c>
-      <c r="AD102" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE102" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>45964</v>
-      </c>
-      <c r="AG102" t="s">
+      <c r="AH102">
+        <v>7060</v>
+      </c>
+      <c r="AI102" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="AH102" t="s">
-        <v>762</v>
-      </c>
-      <c r="AI102" s="3">
-        <v>45961</v>
-      </c>
-      <c r="AJ102" t="s">
-        <v>763</v>
-      </c>
-      <c r="AK102">
-        <v>7060</v>
-      </c>
-      <c r="AL102" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>764</v>
       </c>
       <c r="B103">
         <v>9996621</v>
@@ -14396,100 +14255,91 @@
       <c r="G103" t="s">
         <v>660</v>
       </c>
-      <c r="H103" t="s">
-        <v>661</v>
+      <c r="H103">
+        <v>632556</v>
       </c>
       <c r="I103" t="s">
-        <v>662</v>
-      </c>
-      <c r="J103" t="s">
-        <v>663</v>
-      </c>
-      <c r="K103">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K103" t="s">
+        <v>39</v>
       </c>
       <c r="L103" t="s">
-        <v>38</v>
-      </c>
-      <c r="N103" t="s">
-        <v>39</v>
-      </c>
-      <c r="O103" t="s">
         <v>40</v>
       </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>26</v>
+      </c>
+      <c r="O103">
+        <v>74.75</v>
+      </c>
       <c r="P103">
         <v>0</v>
       </c>
-      <c r="Q103">
-        <v>26</v>
-      </c>
-      <c r="R103">
-        <v>74.75</v>
-      </c>
-      <c r="S103">
-        <v>0</v>
-      </c>
-      <c r="T103" s="1" t="s">
+      <c r="Q103" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="R103" t="s">
+        <v>763</v>
+      </c>
+      <c r="S103" t="s">
+        <v>764</v>
+      </c>
+      <c r="T103">
+        <v>158122</v>
+      </c>
+      <c r="U103" t="s">
         <v>765</v>
       </c>
-      <c r="U103" t="s">
+      <c r="V103">
+        <v>3106200</v>
+      </c>
+      <c r="W103" t="s">
         <v>766</v>
       </c>
-      <c r="V103" t="s">
+      <c r="X103" t="s">
+        <v>517</v>
+      </c>
+      <c r="Y103">
+        <v>26409</v>
+      </c>
+      <c r="Z103" t="s">
         <v>767</v>
       </c>
-      <c r="W103">
-        <v>158122</v>
-      </c>
-      <c r="X103" t="s">
+      <c r="AA103" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB103" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC103" s="3">
+        <v>45959</v>
+      </c>
+      <c r="AD103" t="s">
         <v>768</v>
       </c>
-      <c r="Y103">
-        <v>3106200</v>
-      </c>
-      <c r="Z103" t="s">
+      <c r="AE103" t="s">
         <v>769</v>
       </c>
-      <c r="AA103" t="s">
-        <v>517</v>
-      </c>
-      <c r="AB103">
-        <v>26409</v>
-      </c>
-      <c r="AC103" t="s">
+      <c r="AF103" s="3">
+        <v>45960</v>
+      </c>
+      <c r="AG103" t="s">
         <v>770</v>
       </c>
-      <c r="AD103" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE103" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF103" s="3">
-        <v>45959</v>
-      </c>
-      <c r="AG103" t="s">
-        <v>771</v>
-      </c>
-      <c r="AH103" t="s">
-        <v>772</v>
-      </c>
-      <c r="AI103" s="3">
-        <v>45960</v>
-      </c>
-      <c r="AJ103" t="s">
-        <v>773</v>
-      </c>
-      <c r="AK103">
+      <c r="AH103">
         <v>7060</v>
       </c>
-      <c r="AL103" t="s">
-        <v>670</v>
+      <c r="AI103" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B104">
         <v>9996688</v>
@@ -14509,100 +14359,91 @@
       <c r="G104" t="s">
         <v>660</v>
       </c>
-      <c r="H104" t="s">
-        <v>661</v>
+      <c r="H104">
+        <v>632556</v>
       </c>
       <c r="I104" t="s">
-        <v>662</v>
-      </c>
-      <c r="J104" t="s">
-        <v>663</v>
-      </c>
-      <c r="K104">
-        <v>632556</v>
+        <v>38</v>
+      </c>
+      <c r="K104" t="s">
+        <v>39</v>
       </c>
       <c r="L104" t="s">
-        <v>38</v>
-      </c>
-      <c r="N104" t="s">
-        <v>39</v>
-      </c>
-      <c r="O104" t="s">
         <v>40</v>
       </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>42</v>
+      </c>
+      <c r="O104">
+        <v>74.75</v>
+      </c>
       <c r="P104">
         <v>0</v>
       </c>
-      <c r="Q104">
-        <v>42</v>
-      </c>
-      <c r="R104">
-        <v>74.75</v>
-      </c>
-      <c r="S104">
-        <v>0</v>
-      </c>
-      <c r="T104" s="1" t="s">
+      <c r="Q104" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="R104" t="s">
+        <v>763</v>
+      </c>
+      <c r="S104" t="s">
+        <v>764</v>
+      </c>
+      <c r="T104">
+        <v>158122</v>
+      </c>
+      <c r="U104" t="s">
         <v>765</v>
       </c>
-      <c r="U104" t="s">
+      <c r="V104">
+        <v>3106200</v>
+      </c>
+      <c r="W104" t="s">
         <v>766</v>
       </c>
-      <c r="V104" t="s">
+      <c r="X104" t="s">
+        <v>517</v>
+      </c>
+      <c r="Y104">
+        <v>26409</v>
+      </c>
+      <c r="Z104" t="s">
         <v>767</v>
       </c>
-      <c r="W104">
-        <v>158122</v>
-      </c>
-      <c r="X104" t="s">
+      <c r="AA104" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB104" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC104" s="3">
+        <v>45959</v>
+      </c>
+      <c r="AD104" t="s">
         <v>768</v>
       </c>
-      <c r="Y104">
-        <v>3106200</v>
-      </c>
-      <c r="Z104" t="s">
-        <v>769</v>
-      </c>
-      <c r="AA104" t="s">
-        <v>517</v>
-      </c>
-      <c r="AB104">
-        <v>26409</v>
-      </c>
-      <c r="AC104" t="s">
+      <c r="AE104" t="s">
+        <v>771</v>
+      </c>
+      <c r="AF104" s="3">
+        <v>45960</v>
+      </c>
+      <c r="AG104" t="s">
         <v>770</v>
       </c>
-      <c r="AD104" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE104" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF104" s="3">
-        <v>45959</v>
-      </c>
-      <c r="AG104" t="s">
-        <v>771</v>
-      </c>
-      <c r="AH104" t="s">
-        <v>774</v>
-      </c>
-      <c r="AI104" s="3">
-        <v>45960</v>
-      </c>
-      <c r="AJ104" t="s">
-        <v>773</v>
-      </c>
-      <c r="AK104">
+      <c r="AH104">
         <v>7060</v>
       </c>
-      <c r="AL104" t="s">
-        <v>670</v>
+      <c r="AI104" t="s">
+        <v>667</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B105">
         <v>10756578</v>
@@ -14620,99 +14461,93 @@
         <v>2</v>
       </c>
       <c r="G105" t="s">
+        <v>773</v>
+      </c>
+      <c r="H105">
+        <v>632687</v>
+      </c>
+      <c r="I105" t="s">
+        <v>38</v>
+      </c>
+      <c r="K105" t="s">
+        <v>39</v>
+      </c>
+      <c r="L105" t="s">
+        <v>40</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>11</v>
+      </c>
+      <c r="O105">
+        <v>978.3</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="R105" t="s">
+        <v>775</v>
+      </c>
+      <c r="S105" t="s">
         <v>776</v>
       </c>
-      <c r="H105" t="s">
+      <c r="T105">
+        <v>926149</v>
+      </c>
+      <c r="U105" t="s">
         <v>777</v>
       </c>
-      <c r="I105" t="s">
+      <c r="V105">
+        <v>2700300</v>
+      </c>
+      <c r="W105" t="s">
         <v>778</v>
       </c>
-      <c r="J105">
-        <v>632687</v>
-      </c>
-      <c r="K105" t="s">
-        <v>38</v>
-      </c>
-      <c r="M105" t="s">
-        <v>39</v>
-      </c>
-      <c r="N105" t="s">
-        <v>40</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>11</v>
-      </c>
-      <c r="Q105">
-        <v>978.3</v>
-      </c>
-      <c r="R105">
-        <v>0</v>
-      </c>
-      <c r="S105" s="1" t="s">
+      <c r="X105" t="s">
         <v>779</v>
       </c>
-      <c r="T105" t="s">
+      <c r="Y105">
+        <v>94753</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>777</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC105" s="3">
+        <v>46009</v>
+      </c>
+      <c r="AD105" t="s">
         <v>780</v>
       </c>
-      <c r="U105" t="s">
+      <c r="AE105" t="s">
         <v>781</v>
       </c>
-      <c r="V105">
-        <v>926149</v>
-      </c>
-      <c r="W105" t="s">
+      <c r="AF105" s="3">
+        <v>46044</v>
+      </c>
+      <c r="AG105" t="s">
         <v>782</v>
       </c>
-      <c r="X105">
-        <v>2700300</v>
-      </c>
-      <c r="Y105" t="s">
+      <c r="AH105">
+        <v>7050</v>
+      </c>
+      <c r="AI105" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
         <v>783</v>
-      </c>
-      <c r="Z105" t="s">
-        <v>784</v>
-      </c>
-      <c r="AA105">
-        <v>94753</v>
-      </c>
-      <c r="AB105" t="s">
-        <v>782</v>
-      </c>
-      <c r="AC105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE105" s="3">
-        <v>46009</v>
-      </c>
-      <c r="AF105" t="s">
-        <v>785</v>
-      </c>
-      <c r="AG105" t="s">
-        <v>786</v>
-      </c>
-      <c r="AH105" s="3">
-        <v>46044</v>
-      </c>
-      <c r="AI105" t="s">
-        <v>787</v>
-      </c>
-      <c r="AJ105">
-        <v>7050</v>
-      </c>
-      <c r="AK105" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>788</v>
       </c>
       <c r="B106">
         <v>10700087</v>
@@ -14730,99 +14565,93 @@
         <v>59</v>
       </c>
       <c r="G106" t="s">
-        <v>776</v>
-      </c>
-      <c r="H106" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H106">
+        <v>632687</v>
       </c>
       <c r="I106" t="s">
-        <v>778</v>
-      </c>
-      <c r="J106">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K106" t="s">
-        <v>38</v>
-      </c>
-      <c r="M106" t="s">
         <v>39</v>
       </c>
-      <c r="N106" t="s">
+      <c r="L106" t="s">
         <v>40</v>
       </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>37</v>
+      </c>
       <c r="O106">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="P106">
-        <v>37</v>
-      </c>
-      <c r="Q106">
-        <v>623</v>
-      </c>
-      <c r="R106">
-        <v>0</v>
-      </c>
-      <c r="S106" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="R106" t="s">
+        <v>785</v>
+      </c>
+      <c r="S106" t="s">
+        <v>786</v>
+      </c>
+      <c r="T106">
+        <v>981094</v>
+      </c>
+      <c r="U106" t="s">
+        <v>787</v>
+      </c>
+      <c r="V106">
+        <v>5107743</v>
+      </c>
+      <c r="W106" t="s">
+        <v>788</v>
+      </c>
+      <c r="X106" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y106">
+        <v>97277</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>787</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB106" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC106" s="3">
+        <v>46037</v>
+      </c>
+      <c r="AD106" t="s">
         <v>789</v>
       </c>
-      <c r="T106" t="s">
+      <c r="AE106" t="s">
         <v>790</v>
       </c>
-      <c r="U106" t="s">
+      <c r="AF106" s="3">
+        <v>46037</v>
+      </c>
+      <c r="AG106" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH106">
+        <v>7050</v>
+      </c>
+      <c r="AI106" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="V106">
-        <v>981094</v>
-      </c>
-      <c r="W106" t="s">
-        <v>792</v>
-      </c>
-      <c r="X106">
-        <v>5107743</v>
-      </c>
-      <c r="Y106" t="s">
-        <v>793</v>
-      </c>
-      <c r="Z106" t="s">
-        <v>251</v>
-      </c>
-      <c r="AA106">
-        <v>97277</v>
-      </c>
-      <c r="AB106" t="s">
-        <v>792</v>
-      </c>
-      <c r="AC106" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD106" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE106" s="3">
-        <v>46037</v>
-      </c>
-      <c r="AF106" t="s">
-        <v>794</v>
-      </c>
-      <c r="AG106" t="s">
-        <v>795</v>
-      </c>
-      <c r="AH106" s="3">
-        <v>46037</v>
-      </c>
-      <c r="AI106" t="s">
-        <v>151</v>
-      </c>
-      <c r="AJ106">
-        <v>7050</v>
-      </c>
-      <c r="AK106" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>796</v>
       </c>
       <c r="B107">
         <v>10644023</v>
@@ -14840,99 +14669,93 @@
         <v>4</v>
       </c>
       <c r="G107" t="s">
-        <v>776</v>
-      </c>
-      <c r="H107" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H107">
+        <v>632687</v>
       </c>
       <c r="I107" t="s">
-        <v>778</v>
-      </c>
-      <c r="J107">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K107" t="s">
-        <v>38</v>
-      </c>
-      <c r="M107" t="s">
         <v>39</v>
       </c>
-      <c r="N107" t="s">
+      <c r="L107" t="s">
         <v>40</v>
       </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>2</v>
+      </c>
       <c r="O107">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="P107">
-        <v>2</v>
-      </c>
-      <c r="Q107">
-        <v>720</v>
-      </c>
-      <c r="R107">
-        <v>0</v>
-      </c>
-      <c r="S107" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="R107" t="s">
+        <v>793</v>
+      </c>
+      <c r="S107" t="s">
+        <v>357</v>
+      </c>
+      <c r="T107">
+        <v>930515</v>
+      </c>
+      <c r="U107" t="s">
+        <v>794</v>
+      </c>
+      <c r="V107">
+        <v>3550308</v>
+      </c>
+      <c r="W107" t="s">
+        <v>271</v>
+      </c>
+      <c r="X107" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y107">
+        <v>95556</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB107" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC107" s="3">
+        <v>46029</v>
+      </c>
+      <c r="AD107" t="s">
+        <v>795</v>
+      </c>
+      <c r="AE107" t="s">
+        <v>796</v>
+      </c>
+      <c r="AF107" s="3">
+        <v>46029</v>
+      </c>
+      <c r="AG107" t="s">
         <v>797</v>
       </c>
-      <c r="T107" t="s">
+      <c r="AH107">
+        <v>7050</v>
+      </c>
+      <c r="AI107" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="U107" t="s">
-        <v>357</v>
-      </c>
-      <c r="V107">
-        <v>930515</v>
-      </c>
-      <c r="W107" t="s">
-        <v>799</v>
-      </c>
-      <c r="X107">
-        <v>3550308</v>
-      </c>
-      <c r="Y107" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z107" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA107">
-        <v>95556</v>
-      </c>
-      <c r="AB107" t="s">
-        <v>300</v>
-      </c>
-      <c r="AC107" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD107" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE107" s="3">
-        <v>46029</v>
-      </c>
-      <c r="AF107" t="s">
-        <v>800</v>
-      </c>
-      <c r="AG107" t="s">
-        <v>801</v>
-      </c>
-      <c r="AH107" s="3">
-        <v>46029</v>
-      </c>
-      <c r="AI107" t="s">
-        <v>802</v>
-      </c>
-      <c r="AJ107">
-        <v>7050</v>
-      </c>
-      <c r="AK107" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>803</v>
       </c>
       <c r="B108">
         <v>10617611</v>
@@ -14950,99 +14773,93 @@
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>776</v>
-      </c>
-      <c r="H108" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H108">
+        <v>632687</v>
       </c>
       <c r="I108" t="s">
-        <v>778</v>
-      </c>
-      <c r="J108">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K108" t="s">
-        <v>38</v>
-      </c>
-      <c r="M108" t="s">
         <v>39</v>
       </c>
-      <c r="N108" t="s">
+      <c r="L108" t="s">
         <v>40</v>
       </c>
-      <c r="O108">
-        <v>0</v>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" s="2">
+        <v>48300</v>
       </c>
       <c r="P108">
-        <v>1</v>
-      </c>
-      <c r="Q108" s="2">
-        <v>48300</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="R108" t="s">
+        <v>800</v>
+      </c>
+      <c r="S108" t="s">
+        <v>801</v>
+      </c>
+      <c r="T108">
+        <v>926397</v>
+      </c>
+      <c r="U108" t="s">
+        <v>802</v>
+      </c>
+      <c r="V108">
+        <v>5300108</v>
+      </c>
+      <c r="W108" t="s">
+        <v>71</v>
+      </c>
+      <c r="X108" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y108">
+        <v>25000</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB108" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC108" s="3">
+        <v>46021</v>
+      </c>
+      <c r="AD108" t="s">
         <v>804</v>
       </c>
-      <c r="T108" t="s">
+      <c r="AE108" t="s">
         <v>805</v>
       </c>
-      <c r="U108" t="s">
+      <c r="AF108" s="3">
+        <v>46022</v>
+      </c>
+      <c r="AG108" t="s">
         <v>806</v>
       </c>
-      <c r="V108">
-        <v>926397</v>
-      </c>
-      <c r="W108" t="s">
+      <c r="AH108">
+        <v>7050</v>
+      </c>
+      <c r="AI108" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="X108">
-        <v>5300108</v>
-      </c>
-      <c r="Y108" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z108" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA108">
-        <v>25000</v>
-      </c>
-      <c r="AB108" t="s">
-        <v>808</v>
-      </c>
-      <c r="AC108" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD108" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE108" s="3">
-        <v>46021</v>
-      </c>
-      <c r="AF108" t="s">
-        <v>809</v>
-      </c>
-      <c r="AG108" t="s">
-        <v>810</v>
-      </c>
-      <c r="AH108" s="3">
-        <v>46022</v>
-      </c>
-      <c r="AI108" t="s">
-        <v>811</v>
-      </c>
-      <c r="AJ108">
-        <v>7050</v>
-      </c>
-      <c r="AK108" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="B109">
         <v>10605230</v>
@@ -15060,97 +14877,91 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>776</v>
-      </c>
-      <c r="H109" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H109">
+        <v>632687</v>
       </c>
       <c r="I109" t="s">
-        <v>778</v>
-      </c>
-      <c r="J109">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K109" t="s">
-        <v>38</v>
-      </c>
-      <c r="M109" t="s">
         <v>39</v>
       </c>
-      <c r="N109" t="s">
+      <c r="L109" t="s">
         <v>40</v>
       </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
       <c r="O109">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="P109">
-        <v>2</v>
-      </c>
-      <c r="Q109">
-        <v>349</v>
-      </c>
-      <c r="R109">
-        <v>0</v>
-      </c>
-      <c r="S109" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="R109" t="s">
+        <v>809</v>
+      </c>
+      <c r="S109" t="s">
+        <v>810</v>
+      </c>
+      <c r="T109">
+        <v>373070</v>
+      </c>
+      <c r="U109" t="s">
+        <v>811</v>
+      </c>
+      <c r="V109">
+        <v>4216602</v>
+      </c>
+      <c r="W109" t="s">
+        <v>812</v>
+      </c>
+      <c r="X109" t="s">
         <v>813</v>
       </c>
-      <c r="T109" t="s">
+      <c r="Y109">
+        <v>22201</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>498</v>
+      </c>
+      <c r="AA109" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB109" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC109" s="3">
+        <v>46019</v>
+      </c>
+      <c r="AD109" t="s">
         <v>814</v>
       </c>
-      <c r="U109" t="s">
+      <c r="AE109" t="s">
         <v>815</v>
       </c>
-      <c r="V109">
-        <v>373070</v>
-      </c>
-      <c r="W109" t="s">
+      <c r="AF109" s="3">
+        <v>46020</v>
+      </c>
+      <c r="AG109" t="s">
         <v>816</v>
       </c>
-      <c r="X109">
-        <v>4216602</v>
-      </c>
-      <c r="Y109" t="s">
-        <v>817</v>
-      </c>
-      <c r="Z109" t="s">
-        <v>818</v>
-      </c>
-      <c r="AA109">
-        <v>22201</v>
-      </c>
-      <c r="AB109" t="s">
-        <v>498</v>
-      </c>
-      <c r="AC109" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD109" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE109" s="3">
-        <v>46019</v>
-      </c>
-      <c r="AF109" t="s">
-        <v>819</v>
-      </c>
-      <c r="AG109" t="s">
-        <v>820</v>
-      </c>
-      <c r="AH109" s="3">
-        <v>46020</v>
+      <c r="AH109">
+        <v>7050</v>
       </c>
       <c r="AI109" t="s">
-        <v>821</v>
-      </c>
-      <c r="AJ109">
-        <v>7050</v>
-      </c>
-      <c r="AK109" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>502</v>
       </c>
@@ -15170,99 +14981,93 @@
         <v>33</v>
       </c>
       <c r="G110" t="s">
-        <v>776</v>
-      </c>
-      <c r="H110" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H110">
+        <v>632687</v>
       </c>
       <c r="I110" t="s">
-        <v>778</v>
-      </c>
-      <c r="J110">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K110" t="s">
-        <v>38</v>
-      </c>
-      <c r="M110" t="s">
         <v>39</v>
       </c>
-      <c r="N110" t="s">
+      <c r="L110" t="s">
         <v>40</v>
       </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>10</v>
+      </c>
       <c r="O110">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="P110">
-        <v>10</v>
-      </c>
-      <c r="Q110">
-        <v>760</v>
-      </c>
-      <c r="R110">
-        <v>0</v>
-      </c>
-      <c r="S110" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="T110" t="s">
+      <c r="R110" t="s">
         <v>504</v>
       </c>
+      <c r="S110" t="s">
+        <v>817</v>
+      </c>
+      <c r="T110">
+        <v>983431</v>
+      </c>
       <c r="U110" t="s">
-        <v>822</v>
+        <v>506</v>
       </c>
       <c r="V110">
-        <v>983431</v>
+        <v>2906600</v>
       </c>
       <c r="W110" t="s">
+        <v>507</v>
+      </c>
+      <c r="X110" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y110">
+        <v>95010</v>
+      </c>
+      <c r="Z110" t="s">
         <v>506</v>
       </c>
-      <c r="X110">
-        <v>2906600</v>
-      </c>
-      <c r="Y110" t="s">
-        <v>507</v>
-      </c>
-      <c r="Z110" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA110">
-        <v>95010</v>
+      <c r="AA110" t="s">
+        <v>48</v>
       </c>
       <c r="AB110" t="s">
-        <v>506</v>
-      </c>
-      <c r="AC110" t="s">
-        <v>48</v>
+        <v>140</v>
+      </c>
+      <c r="AC110" s="3">
+        <v>46017</v>
       </c>
       <c r="AD110" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE110" s="3">
+        <v>508</v>
+      </c>
+      <c r="AE110" t="s">
+        <v>818</v>
+      </c>
+      <c r="AF110" s="3">
         <v>46017</v>
       </c>
-      <c r="AF110" t="s">
-        <v>508</v>
-      </c>
       <c r="AG110" t="s">
-        <v>823</v>
-      </c>
-      <c r="AH110" s="3">
-        <v>46017</v>
+        <v>510</v>
+      </c>
+      <c r="AH110">
+        <v>7050</v>
       </c>
       <c r="AI110" t="s">
-        <v>510</v>
-      </c>
-      <c r="AJ110">
-        <v>7050</v>
-      </c>
-      <c r="AK110" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="B111">
         <v>10416308</v>
@@ -15280,99 +15085,93 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>776</v>
-      </c>
-      <c r="H111" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H111">
+        <v>632687</v>
       </c>
       <c r="I111" t="s">
-        <v>778</v>
-      </c>
-      <c r="J111">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K111" t="s">
-        <v>38</v>
-      </c>
-      <c r="M111" t="s">
         <v>39</v>
       </c>
-      <c r="N111" t="s">
+      <c r="L111" t="s">
         <v>40</v>
       </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>12</v>
+      </c>
       <c r="O111">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="P111">
-        <v>12</v>
-      </c>
-      <c r="Q111">
-        <v>508</v>
-      </c>
-      <c r="R111">
-        <v>0</v>
-      </c>
-      <c r="S111" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="R111" t="s">
+        <v>821</v>
+      </c>
+      <c r="S111" t="s">
+        <v>822</v>
+      </c>
+      <c r="T111">
+        <v>986727</v>
+      </c>
+      <c r="U111" t="s">
+        <v>823</v>
+      </c>
+      <c r="V111">
+        <v>3531308</v>
+      </c>
+      <c r="W111" t="s">
+        <v>824</v>
+      </c>
+      <c r="X111" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y111">
+        <v>95933</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>823</v>
+      </c>
+      <c r="AA111" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB111" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC111" s="3">
+        <v>46000</v>
+      </c>
+      <c r="AD111" t="s">
         <v>825</v>
       </c>
-      <c r="T111" t="s">
+      <c r="AE111" t="s">
         <v>826</v>
       </c>
-      <c r="U111" t="s">
+      <c r="AF111" s="3">
+        <v>46000</v>
+      </c>
+      <c r="AG111" t="s">
+        <v>666</v>
+      </c>
+      <c r="AH111">
+        <v>7050</v>
+      </c>
+      <c r="AI111" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="V111">
-        <v>986727</v>
-      </c>
-      <c r="W111" t="s">
-        <v>828</v>
-      </c>
-      <c r="X111">
-        <v>3531308</v>
-      </c>
-      <c r="Y111" t="s">
-        <v>829</v>
-      </c>
-      <c r="Z111" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA111">
-        <v>95933</v>
-      </c>
-      <c r="AB111" t="s">
-        <v>828</v>
-      </c>
-      <c r="AC111" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD111" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE111" s="3">
-        <v>46000</v>
-      </c>
-      <c r="AF111" t="s">
-        <v>830</v>
-      </c>
-      <c r="AG111" t="s">
-        <v>831</v>
-      </c>
-      <c r="AH111" s="3">
-        <v>46000</v>
-      </c>
-      <c r="AI111" t="s">
-        <v>669</v>
-      </c>
-      <c r="AJ111">
-        <v>7050</v>
-      </c>
-      <c r="AK111" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>832</v>
       </c>
       <c r="B112">
         <v>10402215</v>
@@ -15390,99 +15189,93 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>776</v>
-      </c>
-      <c r="H112" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H112">
+        <v>632687</v>
       </c>
       <c r="I112" t="s">
-        <v>778</v>
-      </c>
-      <c r="J112">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K112" t="s">
-        <v>38</v>
-      </c>
-      <c r="M112" t="s">
         <v>39</v>
       </c>
-      <c r="N112" t="s">
+      <c r="L112" t="s">
         <v>40</v>
       </c>
-      <c r="O112">
-        <v>0</v>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>86</v>
+      </c>
+      <c r="O112" s="2">
+        <v>5727.03</v>
       </c>
       <c r="P112">
-        <v>86</v>
-      </c>
-      <c r="Q112" s="2">
-        <v>5727.03</v>
-      </c>
-      <c r="R112">
-        <v>0</v>
-      </c>
-      <c r="S112" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="R112" t="s">
+        <v>829</v>
+      </c>
+      <c r="S112" t="s">
+        <v>830</v>
+      </c>
+      <c r="T112">
+        <v>930618</v>
+      </c>
+      <c r="U112" t="s">
+        <v>831</v>
+      </c>
+      <c r="V112">
+        <v>5300108</v>
+      </c>
+      <c r="W112" t="s">
+        <v>71</v>
+      </c>
+      <c r="X112" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y112">
+        <v>97452</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>831</v>
+      </c>
+      <c r="AA112" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB112" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC112" s="3">
+        <v>45999</v>
+      </c>
+      <c r="AD112" t="s">
+        <v>832</v>
+      </c>
+      <c r="AE112" t="s">
         <v>833</v>
       </c>
-      <c r="T112" t="s">
+      <c r="AF112" s="3">
+        <v>45999</v>
+      </c>
+      <c r="AG112" t="s">
         <v>834</v>
       </c>
-      <c r="U112" t="s">
+      <c r="AH112">
+        <v>7050</v>
+      </c>
+      <c r="AI112" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="113" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="V112">
-        <v>930618</v>
-      </c>
-      <c r="W112" t="s">
-        <v>836</v>
-      </c>
-      <c r="X112">
-        <v>5300108</v>
-      </c>
-      <c r="Y112" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z112" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA112">
-        <v>97452</v>
-      </c>
-      <c r="AB112" t="s">
-        <v>836</v>
-      </c>
-      <c r="AC112" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD112" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE112" s="3">
-        <v>45999</v>
-      </c>
-      <c r="AF112" t="s">
-        <v>837</v>
-      </c>
-      <c r="AG112" t="s">
-        <v>838</v>
-      </c>
-      <c r="AH112" s="3">
-        <v>45999</v>
-      </c>
-      <c r="AI112" t="s">
-        <v>839</v>
-      </c>
-      <c r="AJ112">
-        <v>7050</v>
-      </c>
-      <c r="AK112" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="113" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>840</v>
       </c>
       <c r="B113">
         <v>10230167</v>
@@ -15500,99 +15293,93 @@
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>776</v>
-      </c>
-      <c r="H113" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H113">
+        <v>632687</v>
       </c>
       <c r="I113" t="s">
-        <v>778</v>
-      </c>
-      <c r="J113">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K113" t="s">
-        <v>38</v>
-      </c>
-      <c r="M113" t="s">
         <v>39</v>
       </c>
-      <c r="N113" t="s">
+      <c r="L113" t="s">
         <v>40</v>
       </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
       <c r="O113">
-        <v>0</v>
+        <v>409.39</v>
       </c>
       <c r="P113">
-        <v>2</v>
-      </c>
-      <c r="Q113">
-        <v>409.39</v>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="R113" t="s">
+        <v>837</v>
+      </c>
+      <c r="S113" t="s">
+        <v>365</v>
+      </c>
+      <c r="T113">
+        <v>930938</v>
+      </c>
+      <c r="U113" t="s">
+        <v>838</v>
+      </c>
+      <c r="V113">
+        <v>3552809</v>
+      </c>
+      <c r="W113" t="s">
+        <v>383</v>
+      </c>
+      <c r="X113" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y113">
+        <v>99840</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>838</v>
+      </c>
+      <c r="AA113" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB113" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC113" s="3">
+        <v>45979</v>
+      </c>
+      <c r="AD113" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE113" t="s">
+        <v>840</v>
+      </c>
+      <c r="AF113" s="3">
+        <v>45980</v>
+      </c>
+      <c r="AG113" t="s">
         <v>841</v>
       </c>
-      <c r="T113" t="s">
+      <c r="AH113">
+        <v>7050</v>
+      </c>
+      <c r="AI113" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="114" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
         <v>842</v>
-      </c>
-      <c r="U113" t="s">
-        <v>365</v>
-      </c>
-      <c r="V113">
-        <v>930938</v>
-      </c>
-      <c r="W113" t="s">
-        <v>843</v>
-      </c>
-      <c r="X113">
-        <v>3552809</v>
-      </c>
-      <c r="Y113" t="s">
-        <v>383</v>
-      </c>
-      <c r="Z113" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA113">
-        <v>99840</v>
-      </c>
-      <c r="AB113" t="s">
-        <v>843</v>
-      </c>
-      <c r="AC113" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD113" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE113" s="3">
-        <v>45979</v>
-      </c>
-      <c r="AF113" t="s">
-        <v>844</v>
-      </c>
-      <c r="AG113" t="s">
-        <v>845</v>
-      </c>
-      <c r="AH113" s="3">
-        <v>45980</v>
-      </c>
-      <c r="AI113" t="s">
-        <v>846</v>
-      </c>
-      <c r="AJ113">
-        <v>7050</v>
-      </c>
-      <c r="AK113" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="114" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>847</v>
       </c>
       <c r="B114">
         <v>10224157</v>
@@ -15610,99 +15397,93 @@
         <v>59</v>
       </c>
       <c r="G114" t="s">
-        <v>776</v>
-      </c>
-      <c r="H114" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H114">
+        <v>632687</v>
       </c>
       <c r="I114" t="s">
-        <v>778</v>
-      </c>
-      <c r="J114">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K114" t="s">
-        <v>38</v>
-      </c>
-      <c r="M114" t="s">
         <v>39</v>
       </c>
-      <c r="N114" t="s">
+      <c r="L114" t="s">
         <v>40</v>
       </c>
-      <c r="O114">
-        <v>0</v>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" s="2">
+        <v>3662</v>
       </c>
       <c r="P114">
-        <v>2</v>
-      </c>
-      <c r="Q114" s="2">
-        <v>3662</v>
-      </c>
-      <c r="R114">
-        <v>0</v>
-      </c>
-      <c r="S114" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="T114" t="s">
-        <v>849</v>
+        <v>0</v>
+      </c>
+      <c r="Q114" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="R114" t="s">
+        <v>844</v>
+      </c>
+      <c r="S114" t="s">
+        <v>845</v>
+      </c>
+      <c r="T114">
+        <v>987971</v>
       </c>
       <c r="U114" t="s">
-        <v>850</v>
+        <v>679</v>
       </c>
       <c r="V114">
-        <v>987971</v>
+        <v>4123501</v>
       </c>
       <c r="W114" t="s">
-        <v>682</v>
-      </c>
-      <c r="X114">
-        <v>4123501</v>
-      </c>
-      <c r="Y114" t="s">
-        <v>683</v>
+        <v>680</v>
+      </c>
+      <c r="X114" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y114">
+        <v>98137</v>
       </c>
       <c r="Z114" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA114">
-        <v>98137</v>
+        <v>681</v>
+      </c>
+      <c r="AA114" t="s">
+        <v>48</v>
       </c>
       <c r="AB114" t="s">
-        <v>684</v>
-      </c>
-      <c r="AC114" t="s">
-        <v>48</v>
+        <v>140</v>
+      </c>
+      <c r="AC114" s="3">
+        <v>45980</v>
       </c>
       <c r="AD114" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE114" s="3">
+        <v>846</v>
+      </c>
+      <c r="AE114" t="s">
+        <v>847</v>
+      </c>
+      <c r="AF114" s="3">
         <v>45980</v>
       </c>
-      <c r="AF114" t="s">
-        <v>851</v>
-      </c>
       <c r="AG114" t="s">
-        <v>852</v>
-      </c>
-      <c r="AH114" s="3">
-        <v>45980</v>
+        <v>88</v>
+      </c>
+      <c r="AH114">
+        <v>7050</v>
       </c>
       <c r="AI114" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ114">
-        <v>7050</v>
-      </c>
-      <c r="AK114" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="115" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B115">
         <v>10224156</v>
@@ -15720,99 +15501,93 @@
         <v>58</v>
       </c>
       <c r="G115" t="s">
-        <v>776</v>
-      </c>
-      <c r="H115" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H115">
+        <v>632687</v>
       </c>
       <c r="I115" t="s">
-        <v>778</v>
-      </c>
-      <c r="J115">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K115" t="s">
-        <v>38</v>
-      </c>
-      <c r="M115" t="s">
         <v>39</v>
       </c>
-      <c r="N115" t="s">
+      <c r="L115" t="s">
         <v>40</v>
       </c>
-      <c r="O115">
-        <v>0</v>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>4</v>
+      </c>
+      <c r="O115" s="2">
+        <v>1351.77</v>
       </c>
       <c r="P115">
-        <v>4</v>
-      </c>
-      <c r="Q115" s="2">
-        <v>1351.77</v>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="R115" t="s">
+        <v>844</v>
+      </c>
+      <c r="S115" t="s">
+        <v>845</v>
+      </c>
+      <c r="T115">
+        <v>987971</v>
+      </c>
+      <c r="U115" t="s">
+        <v>679</v>
+      </c>
+      <c r="V115">
+        <v>4123501</v>
+      </c>
+      <c r="W115" t="s">
+        <v>680</v>
+      </c>
+      <c r="X115" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y115">
+        <v>98137</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>681</v>
+      </c>
+      <c r="AA115" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB115" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC115" s="3">
+        <v>45980</v>
+      </c>
+      <c r="AD115" t="s">
+        <v>846</v>
+      </c>
+      <c r="AE115" t="s">
         <v>848</v>
       </c>
-      <c r="T115" t="s">
+      <c r="AF115" s="3">
+        <v>45980</v>
+      </c>
+      <c r="AG115" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH115">
+        <v>7050</v>
+      </c>
+      <c r="AI115" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="116" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="U115" t="s">
-        <v>850</v>
-      </c>
-      <c r="V115">
-        <v>987971</v>
-      </c>
-      <c r="W115" t="s">
-        <v>682</v>
-      </c>
-      <c r="X115">
-        <v>4123501</v>
-      </c>
-      <c r="Y115" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA115">
-        <v>98137</v>
-      </c>
-      <c r="AB115" t="s">
-        <v>684</v>
-      </c>
-      <c r="AC115" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD115" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE115" s="3">
-        <v>45980</v>
-      </c>
-      <c r="AF115" t="s">
-        <v>851</v>
-      </c>
-      <c r="AG115" t="s">
-        <v>853</v>
-      </c>
-      <c r="AH115" s="3">
-        <v>45980</v>
-      </c>
-      <c r="AI115" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ115">
-        <v>7050</v>
-      </c>
-      <c r="AK115" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="116" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>854</v>
       </c>
       <c r="B116">
         <v>10196802</v>
@@ -15830,99 +15605,93 @@
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>776</v>
-      </c>
-      <c r="H116" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="H116">
+        <v>632687</v>
       </c>
       <c r="I116" t="s">
-        <v>778</v>
-      </c>
-      <c r="J116">
-        <v>632687</v>
+        <v>38</v>
       </c>
       <c r="K116" t="s">
-        <v>38</v>
-      </c>
-      <c r="M116" t="s">
         <v>39</v>
       </c>
-      <c r="N116" t="s">
+      <c r="L116" t="s">
         <v>40</v>
       </c>
-      <c r="O116">
-        <v>0</v>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>4</v>
+      </c>
+      <c r="O116" s="2">
+        <v>3359</v>
       </c>
       <c r="P116">
-        <v>4</v>
-      </c>
-      <c r="Q116" s="2">
-        <v>3359</v>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="R116" t="s">
+        <v>851</v>
+      </c>
+      <c r="S116">
+        <v>0</v>
+      </c>
+      <c r="T116">
+        <v>927320</v>
+      </c>
+      <c r="U116" t="s">
+        <v>852</v>
+      </c>
+      <c r="V116">
+        <v>3304557</v>
+      </c>
+      <c r="W116" t="s">
+        <v>106</v>
+      </c>
+      <c r="X116" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y116">
+        <v>38903</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>852</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB116" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC116" s="3">
+        <v>45977</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>853</v>
+      </c>
+      <c r="AE116" t="s">
+        <v>854</v>
+      </c>
+      <c r="AF116" s="3">
+        <v>45978</v>
+      </c>
+      <c r="AG116" t="s">
         <v>855</v>
       </c>
-      <c r="T116" t="s">
+      <c r="AH116">
+        <v>7050</v>
+      </c>
+      <c r="AI116" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="117" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="U116">
-        <v>0</v>
-      </c>
-      <c r="V116">
-        <v>927320</v>
-      </c>
-      <c r="W116" t="s">
-        <v>857</v>
-      </c>
-      <c r="X116">
-        <v>3304557</v>
-      </c>
-      <c r="Y116" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z116" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA116">
-        <v>38903</v>
-      </c>
-      <c r="AB116" t="s">
-        <v>857</v>
-      </c>
-      <c r="AC116" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD116" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE116" s="3">
-        <v>45977</v>
-      </c>
-      <c r="AF116" t="s">
-        <v>858</v>
-      </c>
-      <c r="AG116" t="s">
-        <v>859</v>
-      </c>
-      <c r="AH116" s="3">
-        <v>45978</v>
-      </c>
-      <c r="AI116" t="s">
-        <v>860</v>
-      </c>
-      <c r="AJ116">
-        <v>7050</v>
-      </c>
-      <c r="AK116" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="117" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>861</v>
       </c>
       <c r="B117">
         <v>10773576</v>
@@ -15940,7 +15709,7 @@
         <v>10</v>
       </c>
       <c r="G117" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H117">
         <v>607833</v>
@@ -15967,19 +15736,19 @@
         <v>0</v>
       </c>
       <c r="Q117" s="1" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="R117" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="S117" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="T117">
         <v>740014</v>
       </c>
       <c r="U117" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="V117">
         <v>3304557</v>
@@ -16006,16 +15775,16 @@
         <v>46052</v>
       </c>
       <c r="AD117" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="AE117" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="AF117" s="3">
         <v>46052</v>
       </c>
       <c r="AG117" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="AH117">
         <v>7050</v>
@@ -16024,9 +15793,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="118" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B118">
         <v>10773578</v>
@@ -16044,7 +15813,7 @@
         <v>12</v>
       </c>
       <c r="G118" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H118">
         <v>607833</v>
@@ -16071,19 +15840,19 @@
         <v>0</v>
       </c>
       <c r="Q118" s="1" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="R118" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="S118" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="T118">
         <v>740014</v>
       </c>
       <c r="U118" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="V118">
         <v>3304557</v>
@@ -16110,16 +15879,16 @@
         <v>46052</v>
       </c>
       <c r="AD118" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="AE118" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="AF118" s="3">
         <v>46052</v>
       </c>
       <c r="AG118" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="AH118">
         <v>7050</v>
@@ -16128,9 +15897,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="119" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B119">
         <v>10773577</v>
@@ -16148,7 +15917,7 @@
         <v>11</v>
       </c>
       <c r="G119" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H119">
         <v>607833</v>
@@ -16175,19 +15944,19 @@
         <v>0</v>
       </c>
       <c r="Q119" s="1" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="R119" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="S119" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="T119">
         <v>740014</v>
       </c>
       <c r="U119" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="V119">
         <v>3304557</v>
@@ -16214,16 +15983,16 @@
         <v>46052</v>
       </c>
       <c r="AD119" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="AE119" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="AF119" s="3">
         <v>46052</v>
       </c>
       <c r="AG119" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="AH119">
         <v>7050</v>
@@ -16232,9 +16001,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="120" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B120">
         <v>10465039</v>
@@ -16252,7 +16021,7 @@
         <v>4</v>
       </c>
       <c r="G120" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H120">
         <v>607833</v>
@@ -16279,25 +16048,25 @@
         <v>0</v>
       </c>
       <c r="Q120" s="1" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="R120" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="S120" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T120">
         <v>926188</v>
       </c>
       <c r="U120" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="V120">
         <v>3106200</v>
       </c>
       <c r="W120" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="X120" t="s">
         <v>517</v>
@@ -16306,7 +16075,7 @@
         <v>38636</v>
       </c>
       <c r="Z120" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="AA120" t="s">
         <v>48</v>
@@ -16318,16 +16087,16 @@
         <v>46003</v>
       </c>
       <c r="AD120" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="AE120" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="AF120" s="3">
         <v>46003</v>
       </c>
       <c r="AG120" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="AH120">
         <v>7050</v>
@@ -16336,9 +16105,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="121" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B121">
         <v>10465036</v>
@@ -16356,7 +16125,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H121">
         <v>607833</v>
@@ -16383,25 +16152,25 @@
         <v>0</v>
       </c>
       <c r="Q121" s="1" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="R121" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="S121" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T121">
         <v>926188</v>
       </c>
       <c r="U121" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="V121">
         <v>3106200</v>
       </c>
       <c r="W121" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="X121" t="s">
         <v>517</v>
@@ -16410,7 +16179,7 @@
         <v>38636</v>
       </c>
       <c r="Z121" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="AA121" t="s">
         <v>48</v>
@@ -16422,16 +16191,16 @@
         <v>46003</v>
       </c>
       <c r="AD121" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="AE121" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="AF121" s="3">
         <v>46003</v>
       </c>
       <c r="AG121" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="AH121">
         <v>7050</v>
@@ -16440,9 +16209,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="122" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B122">
         <v>10465038</v>
@@ -16460,7 +16229,7 @@
         <v>3</v>
       </c>
       <c r="G122" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H122">
         <v>607833</v>
@@ -16487,25 +16256,25 @@
         <v>0</v>
       </c>
       <c r="Q122" s="1" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="R122" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="S122" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T122">
         <v>926188</v>
       </c>
       <c r="U122" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="V122">
         <v>3106200</v>
       </c>
       <c r="W122" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="X122" t="s">
         <v>517</v>
@@ -16514,7 +16283,7 @@
         <v>38636</v>
       </c>
       <c r="Z122" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="AA122" t="s">
         <v>48</v>
@@ -16526,16 +16295,16 @@
         <v>46003</v>
       </c>
       <c r="AD122" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="AE122" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="AF122" s="3">
         <v>46003</v>
       </c>
       <c r="AG122" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="AH122">
         <v>7050</v>
@@ -16544,9 +16313,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="123" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B123">
         <v>10192659</v>
@@ -16564,7 +16333,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H123">
         <v>607833</v>
@@ -16591,25 +16360,25 @@
         <v>0</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="R123" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="S123" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="T123">
         <v>389465</v>
       </c>
       <c r="U123" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="V123">
         <v>4314902</v>
       </c>
       <c r="W123" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="X123" t="s">
         <v>194</v>
@@ -16618,7 +16387,7 @@
         <v>38925</v>
       </c>
       <c r="Z123" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="AA123" t="s">
         <v>48</v>
@@ -16630,16 +16399,16 @@
         <v>45978</v>
       </c>
       <c r="AD123" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="AE123" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="AF123" s="3">
         <v>45978</v>
       </c>
       <c r="AG123" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="AH123">
         <v>7050</v>
@@ -16648,9 +16417,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="124" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B124">
         <v>8781031</v>
@@ -16668,7 +16437,7 @@
         <v>12</v>
       </c>
       <c r="G124" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H124">
         <v>607833</v>
@@ -16695,34 +16464,34 @@
         <v>0</v>
       </c>
       <c r="Q124" s="1" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="R124" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="S124" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="T124">
         <v>389452</v>
       </c>
       <c r="U124" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="V124">
         <v>2611606</v>
       </c>
       <c r="W124" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="X124" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="Y124">
         <v>38701</v>
       </c>
       <c r="Z124" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="AA124" t="s">
         <v>48</v>
@@ -16734,16 +16503,16 @@
         <v>45931</v>
       </c>
       <c r="AD124" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="AE124" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="AF124" s="3">
         <v>45931</v>
       </c>
       <c r="AG124" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="AH124">
         <v>7050</v>
@@ -16752,9 +16521,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="125" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="B125">
         <v>9583726</v>
@@ -16772,7 +16541,7 @@
         <v>1</v>
       </c>
       <c r="G125" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H125">
         <v>607833</v>
@@ -16799,34 +16568,34 @@
         <v>0</v>
       </c>
       <c r="Q125" s="1" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="R125" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="S125" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="T125">
         <v>928983</v>
       </c>
       <c r="U125" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="V125">
         <v>2800308</v>
       </c>
       <c r="W125" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="X125" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="Y125">
         <v>38812</v>
       </c>
       <c r="Z125" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="AA125" t="s">
         <v>48</v>
@@ -16838,16 +16607,16 @@
         <v>45923</v>
       </c>
       <c r="AD125" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AE125" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="AF125" s="3">
         <v>45924</v>
       </c>
       <c r="AG125" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="AH125">
         <v>7050</v>
@@ -16856,9 +16625,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="126" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B126">
         <v>8878837</v>
@@ -16876,7 +16645,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H126">
         <v>607833</v>
@@ -16903,19 +16672,19 @@
         <v>0</v>
       </c>
       <c r="Q126" s="1" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="R126" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="S126" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="T126">
         <v>325001</v>
       </c>
       <c r="U126" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="V126">
         <v>3304557</v>
@@ -16930,7 +16699,7 @@
         <v>32314</v>
       </c>
       <c r="Z126" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="AA126" t="s">
         <v>48</v>
@@ -16942,16 +16711,16 @@
         <v>45859</v>
       </c>
       <c r="AD126" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="AE126" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="AF126" s="3">
         <v>45859</v>
       </c>
       <c r="AG126" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="AH126">
         <v>7050</v>
@@ -16960,9 +16729,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="127" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="B127">
         <v>8625687</v>
@@ -16980,7 +16749,7 @@
         <v>5</v>
       </c>
       <c r="G127" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H127">
         <v>607833</v>
@@ -17007,25 +16776,25 @@
         <v>0</v>
       </c>
       <c r="Q127" s="1" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="R127" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="S127" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="T127">
         <v>925163</v>
       </c>
       <c r="U127" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="V127">
         <v>4314902</v>
       </c>
       <c r="W127" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="X127" t="s">
         <v>194</v>
@@ -17034,7 +16803,7 @@
         <v>38930</v>
       </c>
       <c r="Z127" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="AA127" t="s">
         <v>48</v>
@@ -17046,16 +16815,16 @@
         <v>45833</v>
       </c>
       <c r="AD127" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="AE127" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="AF127" s="3">
         <v>45833</v>
       </c>
       <c r="AG127" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="AH127">
         <v>7050</v>
@@ -17064,9 +16833,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="128" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B128">
         <v>8343452</v>
@@ -17084,7 +16853,7 @@
         <v>1</v>
       </c>
       <c r="G128" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H128">
         <v>607833</v>
@@ -17111,37 +16880,37 @@
         <v>0</v>
       </c>
       <c r="Q128" s="1" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="R128" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="S128" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="U128" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="V128">
         <v>2111300</v>
       </c>
       <c r="W128" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="X128" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="Y128">
         <v>14000</v>
       </c>
       <c r="Z128" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="AA128" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="AB128" t="s">
         <v>74</v>
@@ -17150,16 +16919,16 @@
         <v>45804</v>
       </c>
       <c r="AD128" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="AE128" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="AF128" s="3">
         <v>45804</v>
       </c>
       <c r="AG128" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="AH128">
         <v>7050</v>
@@ -17168,9 +16937,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B129">
         <v>8343453</v>
@@ -17188,7 +16957,7 @@
         <v>2</v>
       </c>
       <c r="G129" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H129">
         <v>607833</v>
@@ -17215,37 +16984,37 @@
         <v>0</v>
       </c>
       <c r="Q129" s="1" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="R129" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="S129" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="U129" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="V129">
         <v>2111300</v>
       </c>
       <c r="W129" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="X129" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="Y129">
         <v>14000</v>
       </c>
       <c r="Z129" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="AA129" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="AB129" t="s">
         <v>74</v>
@@ -17254,16 +17023,16 @@
         <v>45804</v>
       </c>
       <c r="AD129" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="AE129" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="AF129" s="3">
         <v>45804</v>
       </c>
       <c r="AG129" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="AH129">
         <v>7050</v>
@@ -17272,9 +17041,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="B130">
         <v>8261185</v>
@@ -17292,7 +17061,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H130">
         <v>607833</v>
@@ -17319,34 +17088,34 @@
         <v>0</v>
       </c>
       <c r="Q130" s="1" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="R130" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="S130" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="T130">
         <v>927487</v>
       </c>
       <c r="U130" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="V130">
         <v>4205407</v>
       </c>
       <c r="W130" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="X130" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="Y130">
         <v>38895</v>
       </c>
       <c r="Z130" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="AA130" t="s">
         <v>48</v>
@@ -17358,16 +17127,16 @@
         <v>45796</v>
       </c>
       <c r="AD130" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="AE130" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="AF130" s="3">
         <v>45796</v>
       </c>
       <c r="AG130" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="AH130">
         <v>7050</v>
@@ -17376,9 +17145,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="B131">
         <v>8261186</v>
@@ -17396,7 +17165,7 @@
         <v>7</v>
       </c>
       <c r="G131" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H131">
         <v>607833</v>
@@ -17423,34 +17192,34 @@
         <v>0</v>
       </c>
       <c r="Q131" s="1" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="R131" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="S131" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="T131">
         <v>927487</v>
       </c>
       <c r="U131" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="V131">
         <v>4205407</v>
       </c>
       <c r="W131" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="X131" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="Y131">
         <v>38895</v>
       </c>
       <c r="Z131" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="AA131" t="s">
         <v>48</v>
@@ -17462,16 +17231,16 @@
         <v>45796</v>
       </c>
       <c r="AD131" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="AE131" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="AF131" s="3">
         <v>45796</v>
       </c>
       <c r="AG131" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="AH131">
         <v>7050</v>
@@ -17480,9 +17249,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B132">
         <v>8156745</v>
@@ -17500,7 +17269,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H132">
         <v>607833</v>
@@ -17527,19 +17296,19 @@
         <v>0</v>
       </c>
       <c r="Q132" s="1" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="R132" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="S132" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T132">
         <v>389136</v>
       </c>
       <c r="U132" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="V132">
         <v>2927408</v>
@@ -17554,7 +17323,7 @@
         <v>38587</v>
       </c>
       <c r="Z132" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="AA132" t="s">
         <v>48</v>
@@ -17566,16 +17335,16 @@
         <v>45784</v>
       </c>
       <c r="AD132" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="AE132" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="AF132" s="3">
         <v>45784</v>
       </c>
       <c r="AG132" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="AH132">
         <v>7050</v>
@@ -17584,9 +17353,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B133">
         <v>8111546</v>
@@ -17604,7 +17373,7 @@
         <v>5</v>
       </c>
       <c r="G133" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H133">
         <v>607833</v>
@@ -17631,34 +17400,34 @@
         <v>0</v>
       </c>
       <c r="Q133" s="1" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="R133" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="S133" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="T133">
         <v>926454</v>
       </c>
       <c r="U133" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="V133">
         <v>2211001</v>
       </c>
       <c r="W133" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="X133" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="Y133">
         <v>94225</v>
       </c>
       <c r="Z133" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="AA133" t="s">
         <v>48</v>
@@ -17670,10 +17439,10 @@
         <v>45776</v>
       </c>
       <c r="AD133" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="AE133" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="AF133" s="3">
         <v>45777</v>
@@ -17688,9 +17457,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="B134">
         <v>7770796</v>
@@ -17708,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H134">
         <v>607833</v>
@@ -17735,34 +17504,34 @@
         <v>0</v>
       </c>
       <c r="Q134" s="1" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="R134" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="S134" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="T134">
         <v>927487</v>
       </c>
       <c r="U134" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="V134">
         <v>4205407</v>
       </c>
       <c r="W134" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="X134" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="Y134">
         <v>38895</v>
       </c>
       <c r="Z134" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="AA134" t="s">
         <v>48</v>
@@ -17774,16 +17543,16 @@
         <v>45741</v>
       </c>
       <c r="AD134" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="AE134" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="AF134" s="3">
         <v>45741</v>
       </c>
       <c r="AG134" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="AH134">
         <v>7050</v>
@@ -17792,9 +17561,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="B135">
         <v>7222959</v>
@@ -17812,7 +17581,7 @@
         <v>2</v>
       </c>
       <c r="G135" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H135">
         <v>607833</v>
@@ -17839,25 +17608,25 @@
         <v>0</v>
       </c>
       <c r="Q135" s="1" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="R135" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="S135" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="T135">
         <v>925543</v>
       </c>
       <c r="U135" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="V135">
         <v>2408003</v>
       </c>
       <c r="W135" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="X135" t="s">
         <v>97</v>
@@ -17866,7 +17635,7 @@
         <v>94462</v>
       </c>
       <c r="Z135" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="AA135" t="s">
         <v>48</v>
@@ -17878,10 +17647,10 @@
         <v>45667</v>
       </c>
       <c r="AD135" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="AE135" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="AF135" s="3">
         <v>45667</v>
@@ -17896,9 +17665,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="B136">
         <v>7222958</v>
@@ -17916,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="G136" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H136">
         <v>607833</v>
@@ -17943,25 +17712,25 @@
         <v>0</v>
       </c>
       <c r="Q136" s="1" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="R136" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="S136" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="T136">
         <v>925543</v>
       </c>
       <c r="U136" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="V136">
         <v>2408003</v>
       </c>
       <c r="W136" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="X136" t="s">
         <v>97</v>
@@ -17970,7 +17739,7 @@
         <v>94462</v>
       </c>
       <c r="Z136" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="AA136" t="s">
         <v>48</v>
@@ -17982,10 +17751,10 @@
         <v>45667</v>
       </c>
       <c r="AD136" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="AE136" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="AF136" s="3">
         <v>45667</v>
@@ -18000,9 +17769,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B137">
         <v>7056148</v>
@@ -18020,7 +17789,7 @@
         <v>2</v>
       </c>
       <c r="G137" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H137">
         <v>607833</v>
@@ -18047,37 +17816,37 @@
         <v>0</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="R137" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="S137" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="T137" s="1" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="U137" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="V137">
         <v>2704302</v>
       </c>
       <c r="W137" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="X137" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="Y137">
         <v>12000</v>
       </c>
       <c r="Z137" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="AA137" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="AB137" t="s">
         <v>74</v>
@@ -18086,16 +17855,16 @@
         <v>45644</v>
       </c>
       <c r="AD137" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="AE137" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="AF137" s="3">
         <v>45644</v>
       </c>
       <c r="AG137" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="AH137">
         <v>7050</v>
@@ -18104,9 +17873,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B138">
         <v>7056147</v>
@@ -18124,7 +17893,7 @@
         <v>1</v>
       </c>
       <c r="G138" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H138">
         <v>607833</v>
@@ -18151,37 +17920,37 @@
         <v>0</v>
       </c>
       <c r="Q138" s="1" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="R138" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="S138" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="T138" s="1" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="U138" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="V138">
         <v>2704302</v>
       </c>
       <c r="W138" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="X138" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="Y138">
         <v>12000</v>
       </c>
       <c r="Z138" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="AA138" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="AB138" t="s">
         <v>74</v>
@@ -18190,16 +17959,16 @@
         <v>45644</v>
       </c>
       <c r="AD138" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="AE138" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="AF138" s="3">
         <v>45644</v>
       </c>
       <c r="AG138" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="AH138">
         <v>7050</v>
@@ -18208,9 +17977,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B139">
         <v>6943814</v>
@@ -18228,7 +17997,7 @@
         <v>2</v>
       </c>
       <c r="G139" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H139">
         <v>607833</v>
@@ -18255,19 +18024,19 @@
         <v>0</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="R139" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="S139" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T139">
         <v>929630</v>
       </c>
       <c r="U139" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="V139">
         <v>3122306</v>
@@ -18282,7 +18051,7 @@
         <v>85277</v>
       </c>
       <c r="Z139" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="AA139" t="s">
         <v>48</v>
@@ -18294,16 +18063,16 @@
         <v>45638</v>
       </c>
       <c r="AD139" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="AE139" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="AF139" s="3">
         <v>45638</v>
       </c>
       <c r="AG139" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="AH139">
         <v>7050</v>
@@ -18312,9 +18081,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B140">
         <v>6790817</v>
@@ -18332,7 +18101,7 @@
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H140">
         <v>607833</v>
@@ -18359,19 +18128,19 @@
         <v>0</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="R140" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="S140" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="T140">
         <v>930222</v>
       </c>
       <c r="U140" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="V140">
         <v>1600303</v>
@@ -18386,7 +18155,7 @@
         <v>39152</v>
       </c>
       <c r="Z140" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="AA140" t="s">
         <v>48</v>
@@ -18398,16 +18167,16 @@
         <v>45628</v>
       </c>
       <c r="AD140" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="AE140" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="AF140" s="3">
         <v>45628</v>
       </c>
       <c r="AG140" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="AH140">
         <v>7050</v>
@@ -18416,9 +18185,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="B141">
         <v>6393495</v>
@@ -18436,7 +18205,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H141">
         <v>607833</v>
@@ -18463,19 +18232,19 @@
         <v>0</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="R141" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="S141" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T141">
         <v>392701</v>
       </c>
       <c r="U141" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="V141">
         <v>3550308</v>
@@ -18490,7 +18259,7 @@
         <v>95508</v>
       </c>
       <c r="Z141" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="AA141" t="s">
         <v>48</v>
@@ -18511,7 +18280,7 @@
         <v>45587</v>
       </c>
       <c r="AG141" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="AH141">
         <v>7050</v>
@@ -18520,9 +18289,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="142" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B142">
         <v>5994839</v>
@@ -18540,7 +18309,7 @@
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H142">
         <v>607833</v>
@@ -18567,37 +18336,37 @@
         <v>0</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="R142" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="S142" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="T142" s="1" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="U142" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="V142">
         <v>2704302</v>
       </c>
       <c r="W142" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="X142" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="Y142">
         <v>14000</v>
       </c>
       <c r="Z142" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="AA142" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="AB142" t="s">
         <v>74</v>
@@ -18606,16 +18375,16 @@
         <v>45566</v>
       </c>
       <c r="AD142" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="AE142" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AF142" s="3">
         <v>45566</v>
       </c>
       <c r="AG142" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="AH142">
         <v>7050</v>
@@ -18624,9 +18393,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B143">
         <v>5022473</v>
@@ -18644,7 +18413,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H143">
         <v>607833</v>
@@ -18671,34 +18440,34 @@
         <v>0</v>
       </c>
       <c r="Q143" s="1" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="R143" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="S143" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="T143">
         <v>389452</v>
       </c>
       <c r="U143" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="V143">
         <v>2611606</v>
       </c>
       <c r="W143" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="X143" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="Y143">
         <v>38701</v>
       </c>
       <c r="Z143" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="AA143" t="s">
         <v>48</v>
@@ -18710,16 +18479,16 @@
         <v>45429</v>
       </c>
       <c r="AD143" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="AE143" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AF143" s="3">
         <v>45429</v>
       </c>
       <c r="AG143" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="AH143">
         <v>7050</v>
@@ -18728,9 +18497,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="B144">
         <v>4072486</v>
@@ -18748,7 +18517,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H144">
         <v>607833</v>
@@ -18775,19 +18544,19 @@
         <v>0</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="R144" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="S144" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T144">
         <v>389136</v>
       </c>
       <c r="U144" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="V144">
         <v>2927408</v>
@@ -18802,7 +18571,7 @@
         <v>38587</v>
       </c>
       <c r="Z144" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="AA144" t="s">
         <v>48</v>
@@ -18814,16 +18583,16 @@
         <v>45260</v>
       </c>
       <c r="AD144" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="AE144" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AF144" s="3">
         <v>45260</v>
       </c>
       <c r="AG144" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="AH144">
         <v>7050</v>
@@ -18832,9 +18601,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B145">
         <v>3924855</v>
@@ -18852,7 +18621,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H145">
         <v>607833</v>
@@ -18879,19 +18648,19 @@
         <v>0</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="R145" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="S145" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T145">
         <v>200346</v>
       </c>
       <c r="U145" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="V145">
         <v>2927408</v>
@@ -18906,7 +18675,7 @@
         <v>30108</v>
       </c>
       <c r="Z145" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="AA145" t="s">
         <v>48</v>
@@ -18918,16 +18687,16 @@
         <v>45239</v>
       </c>
       <c r="AD145" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="AE145" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="AF145" s="3">
         <v>45239</v>
       </c>
       <c r="AG145" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="AH145">
         <v>7050</v>
@@ -18936,9 +18705,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B146">
         <v>3718944</v>
@@ -18956,7 +18725,7 @@
         <v>21</v>
       </c>
       <c r="G146" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H146">
         <v>607833</v>
@@ -18983,19 +18752,19 @@
         <v>0</v>
       </c>
       <c r="Q146" s="1" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="R146" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="S146" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T146">
         <v>926395</v>
       </c>
       <c r="U146" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="V146">
         <v>5103403</v>
@@ -19010,7 +18779,7 @@
         <v>38820</v>
       </c>
       <c r="Z146" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="AA146" t="s">
         <v>48</v>
@@ -19022,16 +18791,16 @@
         <v>45205</v>
       </c>
       <c r="AD146" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="AE146" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="AF146" s="3">
         <v>45205</v>
       </c>
       <c r="AG146" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="AH146">
         <v>7050</v>
@@ -19040,9 +18809,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="B147">
         <v>3614475</v>
@@ -19060,7 +18829,7 @@
         <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H147">
         <v>607833</v>
@@ -19087,19 +18856,19 @@
         <v>0</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="R147" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="S147" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T147">
         <v>160070</v>
       </c>
       <c r="U147" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="V147">
         <v>5300108</v>
@@ -19126,16 +18895,16 @@
         <v>45190</v>
       </c>
       <c r="AD147" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="AE147" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="AF147" s="3">
         <v>45190</v>
       </c>
       <c r="AG147" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="AH147">
         <v>7050</v>
@@ -19144,9 +18913,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B148">
         <v>3601267</v>
@@ -19164,7 +18933,7 @@
         <v>8</v>
       </c>
       <c r="G148" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H148">
         <v>607833</v>
@@ -19191,25 +18960,25 @@
         <v>0</v>
       </c>
       <c r="Q148" s="1" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="R148" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="S148" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="T148">
         <v>929820</v>
       </c>
       <c r="U148" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="V148">
         <v>1504208</v>
       </c>
       <c r="W148" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="X148" t="s">
         <v>148</v>
@@ -19218,7 +18987,7 @@
         <v>99657</v>
       </c>
       <c r="Z148" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="AA148" t="s">
         <v>48</v>
@@ -19230,16 +18999,16 @@
         <v>45189</v>
       </c>
       <c r="AD148" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="AE148" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="AF148" s="3">
         <v>45189</v>
       </c>
       <c r="AG148" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="AH148">
         <v>7050</v>
@@ -19248,9 +19017,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="B149">
         <v>3347163</v>
@@ -19268,7 +19037,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H149">
         <v>607833</v>
@@ -19295,19 +19064,19 @@
         <v>0</v>
       </c>
       <c r="Q149" s="1" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="R149" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="S149" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="T149">
         <v>389336</v>
       </c>
       <c r="U149" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="V149">
         <v>4106902</v>
@@ -19322,7 +19091,7 @@
         <v>38612</v>
       </c>
       <c r="Z149" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="AA149" t="s">
         <v>48</v>
@@ -19334,16 +19103,16 @@
         <v>45148</v>
       </c>
       <c r="AD149" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="AE149" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="AF149" s="3">
         <v>45148</v>
       </c>
       <c r="AG149" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="AH149">
         <v>7050</v>
